--- a/exposures_meta_analysis_final_combined.xlsx
+++ b/exposures_meta_analysis_final_combined.xlsx
@@ -1,25 +1,288 @@
+
+<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
+  <bookViews>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+  </bookViews>
+  <sheets>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+  </sheets>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+</workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="79">
+  <si>
+    <t>Exposure</t>
+  </si>
+  <si>
+    <t>number studies</t>
+  </si>
+  <si>
+    <t>Pooled RR</t>
+  </si>
+  <si>
+    <t>lower CI RR</t>
+  </si>
+  <si>
+    <t>upper CI RR</t>
+  </si>
+  <si>
+    <t>lower PI RR</t>
+  </si>
+  <si>
+    <t>upper PI RR</t>
+  </si>
+  <si>
+    <t>I^2 (%)</t>
+  </si>
+  <si>
+    <t>eggers p-value</t>
+  </si>
+  <si>
+    <t>total N</t>
+  </si>
+  <si>
+    <t>total Cases</t>
+  </si>
+  <si>
+    <t>kefir</t>
+  </si>
+  <si>
+    <t>black_cohosh</t>
+  </si>
+  <si>
+    <t>oats</t>
+  </si>
+  <si>
+    <t>vitamin_b2</t>
+  </si>
+  <si>
+    <t>cesium</t>
+  </si>
+  <si>
+    <t>vitamin_b6</t>
+  </si>
+  <si>
+    <t>quercetin</t>
+  </si>
+  <si>
+    <t>fish_oil</t>
+  </si>
+  <si>
+    <t>grape</t>
+  </si>
+  <si>
+    <t>lutein</t>
+  </si>
+  <si>
+    <t>legumes</t>
+  </si>
+  <si>
+    <t>molybdenum</t>
+  </si>
+  <si>
+    <t>garlic</t>
+  </si>
+  <si>
+    <t>lycopene</t>
+  </si>
+  <si>
+    <t>soy</t>
+  </si>
+  <si>
+    <t>folic_acid</t>
+  </si>
+  <si>
+    <t>pantothenic_acid</t>
+  </si>
+  <si>
+    <t>resveratrol</t>
+  </si>
+  <si>
+    <t>vitamin_b1</t>
+  </si>
+  <si>
+    <t>vitamin_a</t>
+  </si>
+  <si>
+    <t>cod_liver_oil</t>
+  </si>
+  <si>
+    <t>mediterranean_diet</t>
+  </si>
+  <si>
+    <t>olive</t>
+  </si>
+  <si>
+    <t>betaine</t>
+  </si>
+  <si>
+    <t>antioxidants</t>
+  </si>
+  <si>
+    <t>choline</t>
+  </si>
+  <si>
+    <t>beta-carotene</t>
+  </si>
+  <si>
+    <t>magnesium</t>
+  </si>
+  <si>
+    <t>iodine</t>
+  </si>
+  <si>
+    <t>flaxseed</t>
+  </si>
+  <si>
+    <t>vitamin_c</t>
+  </si>
+  <si>
+    <t>flax</t>
+  </si>
+  <si>
+    <t>green_tea</t>
+  </si>
+  <si>
+    <t>copper</t>
+  </si>
+  <si>
+    <t>mushrooms</t>
+  </si>
+  <si>
+    <t>calcium</t>
+  </si>
+  <si>
+    <t>fermented_foods</t>
+  </si>
+  <si>
+    <t>selenium</t>
+  </si>
+  <si>
+    <t>potassium</t>
+  </si>
+  <si>
+    <t>tea</t>
+  </si>
+  <si>
+    <t>vitamin_b12</t>
+  </si>
+  <si>
+    <t>papaya</t>
+  </si>
+  <si>
+    <t>vitamin_e</t>
+  </si>
+  <si>
+    <t>mineral_supplements</t>
+  </si>
+  <si>
+    <t>vitamin_d</t>
+  </si>
+  <si>
+    <t>omega-3_fatty_acids</t>
+  </si>
+  <si>
+    <t>leucine</t>
+  </si>
+  <si>
+    <t>caffeine</t>
+  </si>
+  <si>
+    <t>isoleucine</t>
+  </si>
+  <si>
+    <t>iron</t>
+  </si>
+  <si>
+    <t>conjugated_linoleic_acid</t>
+  </si>
+  <si>
+    <t>bcaas</t>
+  </si>
+  <si>
+    <t>grapefruit</t>
+  </si>
+  <si>
+    <t>creatine</t>
+  </si>
+  <si>
+    <t>glutamine</t>
+  </si>
+  <si>
+    <t>chromium</t>
+  </si>
+  <si>
+    <t>zinc</t>
+  </si>
+  <si>
+    <t>melatonin</t>
+  </si>
+  <si>
+    <t>vitamin_k</t>
+  </si>
+  <si>
+    <t>carnitine</t>
+  </si>
+  <si>
+    <t>dehydroepiandrosterone</t>
+  </si>
+  <si>
+    <t>cannabidiol</t>
+  </si>
+  <si>
+    <t>phosphorus</t>
+  </si>
+  <si>
+    <t>ginseng</t>
+  </si>
+  <si>
+    <t>vitamin_b3</t>
+  </si>
+  <si>
+    <t>omega-6_fatty_acids</t>
+  </si>
+  <si>
+    <t>coenzyme_q10</t>
+  </si>
+  <si>
+    <t>ginkgo</t>
+  </si>
+</sst>
+</file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -27,85 +290,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -390,4 +604,2231 @@
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
+</file>
+
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K69"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>0.34</v>
+      </c>
+      <c r="D2">
+        <v>0.18</v>
+      </c>
+      <c r="E2">
+        <v>0.61</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>34202</v>
+      </c>
+      <c r="K2">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>0.42</v>
+      </c>
+      <c r="D3">
+        <v>0.24</v>
+      </c>
+      <c r="E3">
+        <v>0.73</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>2473</v>
+      </c>
+      <c r="K3">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>0.42</v>
+      </c>
+      <c r="D4">
+        <v>0.21</v>
+      </c>
+      <c r="E4">
+        <v>0.91</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>3326</v>
+      </c>
+      <c r="K4">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>0.48</v>
+      </c>
+      <c r="D5">
+        <v>0.27</v>
+      </c>
+      <c r="E5">
+        <v>0.84</v>
+      </c>
+      <c r="F5">
+        <v>0.04</v>
+      </c>
+      <c r="G5">
+        <v>5.85</v>
+      </c>
+      <c r="H5">
+        <v>83.7</v>
+      </c>
+      <c r="I5">
+        <v>0.06298647397409918</v>
+      </c>
+      <c r="J5">
+        <v>32399</v>
+      </c>
+      <c r="K5">
+        <v>1754</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>0.53</v>
+      </c>
+      <c r="D6">
+        <v>0.33</v>
+      </c>
+      <c r="E6">
+        <v>0.84</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>486</v>
+      </c>
+      <c r="K6">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7">
+        <v>9</v>
+      </c>
+      <c r="C7">
+        <v>0.57</v>
+      </c>
+      <c r="D7">
+        <v>0.45</v>
+      </c>
+      <c r="E7">
+        <v>0.72</v>
+      </c>
+      <c r="F7">
+        <v>0.28</v>
+      </c>
+      <c r="G7">
+        <v>1.16</v>
+      </c>
+      <c r="H7">
+        <v>64</v>
+      </c>
+      <c r="I7">
+        <v>0.006731396185093079</v>
+      </c>
+      <c r="J7">
+        <v>93349</v>
+      </c>
+      <c r="K7">
+        <v>3573</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8">
+        <v>0.58</v>
+      </c>
+      <c r="D8">
+        <v>0.41</v>
+      </c>
+      <c r="E8">
+        <v>0.8</v>
+      </c>
+      <c r="F8">
+        <v>0.2</v>
+      </c>
+      <c r="G8">
+        <v>1.68</v>
+      </c>
+      <c r="H8">
+        <v>80.5</v>
+      </c>
+      <c r="I8">
+        <v>0.3786419082402221</v>
+      </c>
+      <c r="J8">
+        <v>104205</v>
+      </c>
+      <c r="K8">
+        <v>4158</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9">
+        <v>9</v>
+      </c>
+      <c r="C9">
+        <v>0.6</v>
+      </c>
+      <c r="D9">
+        <v>0.49</v>
+      </c>
+      <c r="E9">
+        <v>0.73</v>
+      </c>
+      <c r="F9">
+        <v>0.36</v>
+      </c>
+      <c r="G9">
+        <v>0.99</v>
+      </c>
+      <c r="H9">
+        <v>45.8</v>
+      </c>
+      <c r="I9">
+        <v>0.001436693272278808</v>
+      </c>
+      <c r="J9">
+        <v>44287</v>
+      </c>
+      <c r="K9">
+        <v>4380</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>0.62</v>
+      </c>
+      <c r="D10">
+        <v>0.38</v>
+      </c>
+      <c r="E10">
+        <v>0.96</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>1067</v>
+      </c>
+      <c r="K10">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11">
+        <v>12</v>
+      </c>
+      <c r="C11">
+        <v>0.63</v>
+      </c>
+      <c r="D11">
+        <v>0.53</v>
+      </c>
+      <c r="E11">
+        <v>0.75</v>
+      </c>
+      <c r="F11">
+        <v>0.35</v>
+      </c>
+      <c r="G11">
+        <v>1.14</v>
+      </c>
+      <c r="H11">
+        <v>79.7</v>
+      </c>
+      <c r="I11">
+        <v>0.0005316569676412729</v>
+      </c>
+      <c r="J11">
+        <v>1072888</v>
+      </c>
+      <c r="K11">
+        <v>50483</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12">
+        <v>24</v>
+      </c>
+      <c r="C12">
+        <v>0.65</v>
+      </c>
+      <c r="D12">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E12">
+        <v>0.75</v>
+      </c>
+      <c r="F12">
+        <v>0.32</v>
+      </c>
+      <c r="G12">
+        <v>1.29</v>
+      </c>
+      <c r="H12">
+        <v>94.5</v>
+      </c>
+      <c r="I12">
+        <v>0.000257543849298683</v>
+      </c>
+      <c r="J12">
+        <v>427826</v>
+      </c>
+      <c r="K12">
+        <v>26639</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13">
+        <v>3</v>
+      </c>
+      <c r="C13">
+        <v>0.66</v>
+      </c>
+      <c r="D13">
+        <v>0.47</v>
+      </c>
+      <c r="E13">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F13">
+        <v>0.02</v>
+      </c>
+      <c r="G13">
+        <v>29.2</v>
+      </c>
+      <c r="H13">
+        <v>81.5</v>
+      </c>
+      <c r="I13">
+        <v>0.8859576999282144</v>
+      </c>
+      <c r="J13">
+        <v>3215</v>
+      </c>
+      <c r="K13">
+        <v>2330</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14">
+        <v>5</v>
+      </c>
+      <c r="C14">
+        <v>0.67</v>
+      </c>
+      <c r="D14">
+        <v>0.51</v>
+      </c>
+      <c r="E14">
+        <v>0.89</v>
+      </c>
+      <c r="F14">
+        <v>0.3</v>
+      </c>
+      <c r="G14">
+        <v>1.51</v>
+      </c>
+      <c r="H14">
+        <v>45.9</v>
+      </c>
+      <c r="I14">
+        <v>0.05697747501723408</v>
+      </c>
+      <c r="J14">
+        <v>245262</v>
+      </c>
+      <c r="K14">
+        <v>2081</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15">
+        <v>16</v>
+      </c>
+      <c r="C15">
+        <v>0.68</v>
+      </c>
+      <c r="D15">
+        <v>0.59</v>
+      </c>
+      <c r="E15">
+        <v>0.78</v>
+      </c>
+      <c r="F15">
+        <v>0.42</v>
+      </c>
+      <c r="G15">
+        <v>1.09</v>
+      </c>
+      <c r="H15">
+        <v>73.7</v>
+      </c>
+      <c r="I15">
+        <v>0.002415943955796325</v>
+      </c>
+      <c r="J15">
+        <v>403398</v>
+      </c>
+      <c r="K15">
+        <v>138088</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16">
+        <v>51</v>
+      </c>
+      <c r="C16">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="D16">
+        <v>0.61</v>
+      </c>
+      <c r="E16">
+        <v>0.77</v>
+      </c>
+      <c r="F16">
+        <v>0.33</v>
+      </c>
+      <c r="G16">
+        <v>1.46</v>
+      </c>
+      <c r="H16">
+        <v>89.8</v>
+      </c>
+      <c r="I16">
+        <v>8.642473771776249E-05</v>
+      </c>
+      <c r="J16">
+        <v>935678</v>
+      </c>
+      <c r="K16">
+        <v>44156</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17">
+        <v>44</v>
+      </c>
+      <c r="C17">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="D17">
+        <v>0.6</v>
+      </c>
+      <c r="E17">
+        <v>0.79</v>
+      </c>
+      <c r="F17">
+        <v>0.3</v>
+      </c>
+      <c r="G17">
+        <v>1.56</v>
+      </c>
+      <c r="H17">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="I17">
+        <v>0.002795251156589609</v>
+      </c>
+      <c r="J17">
+        <v>1145101</v>
+      </c>
+      <c r="K17">
+        <v>55988</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>0.73</v>
+      </c>
+      <c r="D18">
+        <v>0.53</v>
+      </c>
+      <c r="E18">
+        <v>0.97</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>969</v>
+      </c>
+      <c r="K18">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19">
+        <v>0.73</v>
+      </c>
+      <c r="D19">
+        <v>0.59</v>
+      </c>
+      <c r="E19">
+        <v>0.9</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>3049</v>
+      </c>
+      <c r="K19">
+        <v>1472</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20">
+        <v>2</v>
+      </c>
+      <c r="C20">
+        <v>0.75</v>
+      </c>
+      <c r="D20">
+        <v>0.61</v>
+      </c>
+      <c r="E20">
+        <v>0.93</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>38639</v>
+      </c>
+      <c r="K20">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21">
+        <v>31</v>
+      </c>
+      <c r="C21">
+        <v>0.76</v>
+      </c>
+      <c r="D21">
+        <v>0.68</v>
+      </c>
+      <c r="E21">
+        <v>0.86</v>
+      </c>
+      <c r="F21">
+        <v>0.41</v>
+      </c>
+      <c r="G21">
+        <v>1.4</v>
+      </c>
+      <c r="H21">
+        <v>87</v>
+      </c>
+      <c r="I21">
+        <v>0.002638377402642224</v>
+      </c>
+      <c r="J21">
+        <v>1617624</v>
+      </c>
+      <c r="K21">
+        <v>201586</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22">
+        <v>2</v>
+      </c>
+      <c r="C22">
+        <v>0.78</v>
+      </c>
+      <c r="D22">
+        <v>0.68</v>
+      </c>
+      <c r="E22">
+        <v>0.9</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>4001</v>
+      </c>
+      <c r="K22">
+        <v>1731</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23">
+        <v>30</v>
+      </c>
+      <c r="C23">
+        <v>0.78</v>
+      </c>
+      <c r="D23">
+        <v>0.73</v>
+      </c>
+      <c r="E23">
+        <v>0.84</v>
+      </c>
+      <c r="F23">
+        <v>0.59</v>
+      </c>
+      <c r="G23">
+        <v>1.04</v>
+      </c>
+      <c r="H23">
+        <v>75</v>
+      </c>
+      <c r="I23">
+        <v>7.761396614455931E-08</v>
+      </c>
+      <c r="J23">
+        <v>704747</v>
+      </c>
+      <c r="K23">
+        <v>38713</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24">
+        <v>23</v>
+      </c>
+      <c r="C24">
+        <v>0.79</v>
+      </c>
+      <c r="D24">
+        <v>0.72</v>
+      </c>
+      <c r="E24">
+        <v>0.87</v>
+      </c>
+      <c r="F24">
+        <v>0.54</v>
+      </c>
+      <c r="G24">
+        <v>1.16</v>
+      </c>
+      <c r="H24">
+        <v>77.2</v>
+      </c>
+      <c r="I24">
+        <v>0.0006440340038630955</v>
+      </c>
+      <c r="J24">
+        <v>269814</v>
+      </c>
+      <c r="K24">
+        <v>26539</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B25">
+        <v>5</v>
+      </c>
+      <c r="C25">
+        <v>0.79</v>
+      </c>
+      <c r="D25">
+        <v>0.64</v>
+      </c>
+      <c r="E25">
+        <v>0.97</v>
+      </c>
+      <c r="F25">
+        <v>0.4</v>
+      </c>
+      <c r="G25">
+        <v>1.57</v>
+      </c>
+      <c r="H25">
+        <v>70.5</v>
+      </c>
+      <c r="I25">
+        <v>0.03910415220711942</v>
+      </c>
+      <c r="J25">
+        <v>94899</v>
+      </c>
+      <c r="K25">
+        <v>6188</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" t="s">
+        <v>35</v>
+      </c>
+      <c r="B26">
+        <v>25</v>
+      </c>
+      <c r="C26">
+        <v>0.8</v>
+      </c>
+      <c r="D26">
+        <v>0.72</v>
+      </c>
+      <c r="E26">
+        <v>0.89</v>
+      </c>
+      <c r="F26">
+        <v>0.54</v>
+      </c>
+      <c r="G26">
+        <v>1.2</v>
+      </c>
+      <c r="H26">
+        <v>79.3</v>
+      </c>
+      <c r="I26">
+        <v>0.04854113710133826</v>
+      </c>
+      <c r="J26">
+        <v>606881</v>
+      </c>
+      <c r="K26">
+        <v>261052</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" t="s">
+        <v>36</v>
+      </c>
+      <c r="B27">
+        <v>7</v>
+      </c>
+      <c r="C27">
+        <v>0.8</v>
+      </c>
+      <c r="D27">
+        <v>0.62</v>
+      </c>
+      <c r="E27">
+        <v>1.04</v>
+      </c>
+      <c r="F27">
+        <v>0.34</v>
+      </c>
+      <c r="G27">
+        <v>1.89</v>
+      </c>
+      <c r="H27">
+        <v>83</v>
+      </c>
+      <c r="I27">
+        <v>0.112119108811728</v>
+      </c>
+      <c r="J27">
+        <v>99109</v>
+      </c>
+      <c r="K27">
+        <v>8266</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28">
+        <v>53</v>
+      </c>
+      <c r="C28">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="D28">
+        <v>0.71</v>
+      </c>
+      <c r="E28">
+        <v>0.91</v>
+      </c>
+      <c r="F28">
+        <v>0.35</v>
+      </c>
+      <c r="G28">
+        <v>1.83</v>
+      </c>
+      <c r="H28">
+        <v>93.5</v>
+      </c>
+      <c r="I28">
+        <v>0.2779507323699855</v>
+      </c>
+      <c r="J28">
+        <v>1684109</v>
+      </c>
+      <c r="K28">
+        <v>104765</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29">
+        <v>14</v>
+      </c>
+      <c r="C29">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="D29">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E29">
+        <v>0.95</v>
+      </c>
+      <c r="F29">
+        <v>0.46</v>
+      </c>
+      <c r="G29">
+        <v>1.42</v>
+      </c>
+      <c r="H29">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="I29">
+        <v>0.0005795809350502423</v>
+      </c>
+      <c r="J29">
+        <v>1134079</v>
+      </c>
+      <c r="K29">
+        <v>146180</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30">
+        <v>13</v>
+      </c>
+      <c r="C30">
+        <v>0.83</v>
+      </c>
+      <c r="D30">
+        <v>0.5</v>
+      </c>
+      <c r="E30">
+        <v>1.39</v>
+      </c>
+      <c r="F30">
+        <v>0.12</v>
+      </c>
+      <c r="G30">
+        <v>6.05</v>
+      </c>
+      <c r="H30">
+        <v>98.3</v>
+      </c>
+      <c r="I30">
+        <v>0.2623242622855663</v>
+      </c>
+      <c r="J30">
+        <v>261271</v>
+      </c>
+      <c r="K30">
+        <v>9445</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31">
+        <v>1</v>
+      </c>
+      <c r="C31">
+        <v>0.84</v>
+      </c>
+      <c r="D31">
+        <v>0.72</v>
+      </c>
+      <c r="E31">
+        <v>0.97</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>6299</v>
+      </c>
+      <c r="K31">
+        <v>2999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32">
+        <v>28</v>
+      </c>
+      <c r="C32">
+        <v>0.84</v>
+      </c>
+      <c r="D32">
+        <v>0.74</v>
+      </c>
+      <c r="E32">
+        <v>0.96</v>
+      </c>
+      <c r="F32">
+        <v>0.46</v>
+      </c>
+      <c r="G32">
+        <v>1.55</v>
+      </c>
+      <c r="H32">
+        <v>87.40000000000001</v>
+      </c>
+      <c r="I32">
+        <v>0.1658558104216727</v>
+      </c>
+      <c r="J32">
+        <v>497189</v>
+      </c>
+      <c r="K32">
+        <v>36327</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33">
+        <v>1</v>
+      </c>
+      <c r="C33">
+        <v>0.84</v>
+      </c>
+      <c r="D33">
+        <v>0.72</v>
+      </c>
+      <c r="E33">
+        <v>0.97</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>6369</v>
+      </c>
+      <c r="K33">
+        <v>2999</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34">
+        <v>44</v>
+      </c>
+      <c r="C34">
+        <v>0.85</v>
+      </c>
+      <c r="D34">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E34">
+        <v>0.89</v>
+      </c>
+      <c r="F34">
+        <v>0.67</v>
+      </c>
+      <c r="G34">
+        <v>1.07</v>
+      </c>
+      <c r="H34">
+        <v>86.90000000000001</v>
+      </c>
+      <c r="I34">
+        <v>6.802984271605328E-06</v>
+      </c>
+      <c r="J34">
+        <v>4809089</v>
+      </c>
+      <c r="K34">
+        <v>311206</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35" t="s">
+        <v>44</v>
+      </c>
+      <c r="B35">
+        <v>8</v>
+      </c>
+      <c r="C35">
+        <v>0.86</v>
+      </c>
+      <c r="D35">
+        <v>0.67</v>
+      </c>
+      <c r="E35">
+        <v>1.09</v>
+      </c>
+      <c r="F35">
+        <v>0.38</v>
+      </c>
+      <c r="G35">
+        <v>1.95</v>
+      </c>
+      <c r="H35">
+        <v>87</v>
+      </c>
+      <c r="I35">
+        <v>0.2524762887623844</v>
+      </c>
+      <c r="J35">
+        <v>97079</v>
+      </c>
+      <c r="K35">
+        <v>10555</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
+      <c r="A36" t="s">
+        <v>45</v>
+      </c>
+      <c r="B36">
+        <v>6</v>
+      </c>
+      <c r="C36">
+        <v>0.87</v>
+      </c>
+      <c r="D36">
+        <v>0.39</v>
+      </c>
+      <c r="E36">
+        <v>1.93</v>
+      </c>
+      <c r="F36">
+        <v>0.05</v>
+      </c>
+      <c r="G36">
+        <v>15.78</v>
+      </c>
+      <c r="H36">
+        <v>93.8</v>
+      </c>
+      <c r="I36">
+        <v>0.2932388285196719</v>
+      </c>
+      <c r="J36">
+        <v>4444</v>
+      </c>
+      <c r="K36">
+        <v>2146</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37" t="s">
+        <v>46</v>
+      </c>
+      <c r="B37">
+        <v>10</v>
+      </c>
+      <c r="C37">
+        <v>0.87</v>
+      </c>
+      <c r="D37">
+        <v>0.77</v>
+      </c>
+      <c r="E37">
+        <v>0.99</v>
+      </c>
+      <c r="F37">
+        <v>0.58</v>
+      </c>
+      <c r="G37">
+        <v>1.3</v>
+      </c>
+      <c r="H37">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="I37">
+        <v>0.2291820306546928</v>
+      </c>
+      <c r="J37">
+        <v>179879</v>
+      </c>
+      <c r="K37">
+        <v>11354</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11">
+      <c r="A38" t="s">
+        <v>47</v>
+      </c>
+      <c r="B38">
+        <v>8</v>
+      </c>
+      <c r="C38">
+        <v>0.89</v>
+      </c>
+      <c r="D38">
+        <v>0.77</v>
+      </c>
+      <c r="E38">
+        <v>1.04</v>
+      </c>
+      <c r="F38">
+        <v>0.6</v>
+      </c>
+      <c r="G38">
+        <v>1.34</v>
+      </c>
+      <c r="H38">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="I38">
+        <v>0.5466234157697405</v>
+      </c>
+      <c r="J38">
+        <v>92433</v>
+      </c>
+      <c r="K38">
+        <v>41077</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11">
+      <c r="A39" t="s">
+        <v>48</v>
+      </c>
+      <c r="B39">
+        <v>18</v>
+      </c>
+      <c r="C39">
+        <v>0.9</v>
+      </c>
+      <c r="D39">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E39">
+        <v>0.99</v>
+      </c>
+      <c r="F39">
+        <v>0.67</v>
+      </c>
+      <c r="G39">
+        <v>1.2</v>
+      </c>
+      <c r="H39">
+        <v>63</v>
+      </c>
+      <c r="I39">
+        <v>0.2901421475330361</v>
+      </c>
+      <c r="J39">
+        <v>272285</v>
+      </c>
+      <c r="K39">
+        <v>19806</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11">
+      <c r="A40" t="s">
+        <v>49</v>
+      </c>
+      <c r="B40">
+        <v>6</v>
+      </c>
+      <c r="C40">
+        <v>0.91</v>
+      </c>
+      <c r="D40">
+        <v>0.7</v>
+      </c>
+      <c r="E40">
+        <v>1.19</v>
+      </c>
+      <c r="F40">
+        <v>0.37</v>
+      </c>
+      <c r="G40">
+        <v>2.26</v>
+      </c>
+      <c r="H40">
+        <v>87.40000000000001</v>
+      </c>
+      <c r="I40">
+        <v>0.04813316803355388</v>
+      </c>
+      <c r="J40">
+        <v>152583</v>
+      </c>
+      <c r="K40">
+        <v>4518</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11">
+      <c r="A41" t="s">
+        <v>50</v>
+      </c>
+      <c r="B41">
+        <v>29</v>
+      </c>
+      <c r="C41">
+        <v>0.92</v>
+      </c>
+      <c r="D41">
+        <v>0.85</v>
+      </c>
+      <c r="E41">
+        <v>1</v>
+      </c>
+      <c r="F41">
+        <v>0.65</v>
+      </c>
+      <c r="G41">
+        <v>1.3</v>
+      </c>
+      <c r="H41">
+        <v>91.3</v>
+      </c>
+      <c r="I41">
+        <v>0.2680600037631445</v>
+      </c>
+      <c r="J41">
+        <v>957499</v>
+      </c>
+      <c r="K41">
+        <v>159300</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11">
+      <c r="A42" t="s">
+        <v>51</v>
+      </c>
+      <c r="B42">
+        <v>9</v>
+      </c>
+      <c r="C42">
+        <v>0.93</v>
+      </c>
+      <c r="D42">
+        <v>0.76</v>
+      </c>
+      <c r="E42">
+        <v>1.13</v>
+      </c>
+      <c r="F42">
+        <v>0.49</v>
+      </c>
+      <c r="G42">
+        <v>1.75</v>
+      </c>
+      <c r="H42">
+        <v>83.90000000000001</v>
+      </c>
+      <c r="I42">
+        <v>0.01172932257602494</v>
+      </c>
+      <c r="J42">
+        <v>1016977</v>
+      </c>
+      <c r="K42">
+        <v>144078</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11">
+      <c r="A43" t="s">
+        <v>52</v>
+      </c>
+      <c r="B43">
+        <v>2</v>
+      </c>
+      <c r="C43">
+        <v>0.93</v>
+      </c>
+      <c r="D43">
+        <v>0.36</v>
+      </c>
+      <c r="E43">
+        <v>2.41</v>
+      </c>
+      <c r="H43">
+        <v>93.3</v>
+      </c>
+      <c r="J43">
+        <v>1221</v>
+      </c>
+      <c r="K43">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11">
+      <c r="A44" t="s">
+        <v>53</v>
+      </c>
+      <c r="B44">
+        <v>19</v>
+      </c>
+      <c r="C44">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="D44">
+        <v>0.8</v>
+      </c>
+      <c r="E44">
+        <v>1.11</v>
+      </c>
+      <c r="F44">
+        <v>0.49</v>
+      </c>
+      <c r="G44">
+        <v>1.82</v>
+      </c>
+      <c r="H44">
+        <v>85.3</v>
+      </c>
+      <c r="I44">
+        <v>0.9404741555184667</v>
+      </c>
+      <c r="J44">
+        <v>651545</v>
+      </c>
+      <c r="K44">
+        <v>267660</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11">
+      <c r="A45" t="s">
+        <v>54</v>
+      </c>
+      <c r="B45">
+        <v>72</v>
+      </c>
+      <c r="C45">
+        <v>0.96</v>
+      </c>
+      <c r="D45">
+        <v>0.9</v>
+      </c>
+      <c r="E45">
+        <v>1.02</v>
+      </c>
+      <c r="F45">
+        <v>0.64</v>
+      </c>
+      <c r="G45">
+        <v>1.44</v>
+      </c>
+      <c r="H45">
+        <v>88.3</v>
+      </c>
+      <c r="I45">
+        <v>0.5957092118313954</v>
+      </c>
+      <c r="J45">
+        <v>2700805</v>
+      </c>
+      <c r="K45">
+        <v>341285</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11">
+      <c r="A46" t="s">
+        <v>55</v>
+      </c>
+      <c r="B46">
+        <v>100</v>
+      </c>
+      <c r="C46">
+        <v>0.99</v>
+      </c>
+      <c r="D46">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E46">
+        <v>1.05</v>
+      </c>
+      <c r="F46">
+        <v>0.62</v>
+      </c>
+      <c r="G46">
+        <v>1.6</v>
+      </c>
+      <c r="H46">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="I46">
+        <v>0.2320019333708043</v>
+      </c>
+      <c r="J46">
+        <v>1210207</v>
+      </c>
+      <c r="K46">
+        <v>125881</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11">
+      <c r="A47" t="s">
+        <v>56</v>
+      </c>
+      <c r="B47">
+        <v>5</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
+      <c r="D47">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E47">
+        <v>1.25</v>
+      </c>
+      <c r="F47">
+        <v>0.51</v>
+      </c>
+      <c r="G47">
+        <v>1.98</v>
+      </c>
+      <c r="H47">
+        <v>83.3</v>
+      </c>
+      <c r="I47">
+        <v>0.4046396073872831</v>
+      </c>
+      <c r="J47">
+        <v>404028</v>
+      </c>
+      <c r="K47">
+        <v>9298</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11">
+      <c r="A48" t="s">
+        <v>57</v>
+      </c>
+      <c r="B48">
+        <v>4</v>
+      </c>
+      <c r="C48">
+        <v>1.01</v>
+      </c>
+      <c r="D48">
+        <v>0.91</v>
+      </c>
+      <c r="E48">
+        <v>1.13</v>
+      </c>
+      <c r="F48">
+        <v>0.65</v>
+      </c>
+      <c r="G48">
+        <v>1.57</v>
+      </c>
+      <c r="H48">
+        <v>80.8</v>
+      </c>
+      <c r="I48">
+        <v>0.5613202208181793</v>
+      </c>
+      <c r="J48">
+        <v>225687</v>
+      </c>
+      <c r="K48">
+        <v>14912</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11">
+      <c r="A49" t="s">
+        <v>58</v>
+      </c>
+      <c r="B49">
+        <v>15</v>
+      </c>
+      <c r="C49">
+        <v>1.01</v>
+      </c>
+      <c r="D49">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E49">
+        <v>1.09</v>
+      </c>
+      <c r="F49">
+        <v>0.78</v>
+      </c>
+      <c r="G49">
+        <v>1.31</v>
+      </c>
+      <c r="H49">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="I49">
+        <v>0.6418968892061229</v>
+      </c>
+      <c r="J49">
+        <v>650466</v>
+      </c>
+      <c r="K49">
+        <v>35940</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11">
+      <c r="A50" t="s">
+        <v>59</v>
+      </c>
+      <c r="B50">
+        <v>5</v>
+      </c>
+      <c r="C50">
+        <v>1.04</v>
+      </c>
+      <c r="D50">
+        <v>0.9</v>
+      </c>
+      <c r="E50">
+        <v>1.2</v>
+      </c>
+      <c r="F50">
+        <v>0.64</v>
+      </c>
+      <c r="G50">
+        <v>1.67</v>
+      </c>
+      <c r="H50">
+        <v>87.40000000000001</v>
+      </c>
+      <c r="I50">
+        <v>0.725350927199553</v>
+      </c>
+      <c r="J50">
+        <v>227161</v>
+      </c>
+      <c r="K50">
+        <v>15765</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11">
+      <c r="A51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B51">
+        <v>48</v>
+      </c>
+      <c r="C51">
+        <v>1.05</v>
+      </c>
+      <c r="D51">
+        <v>0.97</v>
+      </c>
+      <c r="E51">
+        <v>1.13</v>
+      </c>
+      <c r="F51">
+        <v>0.68</v>
+      </c>
+      <c r="G51">
+        <v>1.62</v>
+      </c>
+      <c r="H51">
+        <v>93.2</v>
+      </c>
+      <c r="I51">
+        <v>0.1005460482114157</v>
+      </c>
+      <c r="J51">
+        <v>1080429</v>
+      </c>
+      <c r="K51">
+        <v>181363</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11">
+      <c r="A52" t="s">
+        <v>61</v>
+      </c>
+      <c r="B52">
+        <v>4</v>
+      </c>
+      <c r="C52">
+        <v>1.06</v>
+      </c>
+      <c r="D52">
+        <v>0.92</v>
+      </c>
+      <c r="E52">
+        <v>1.22</v>
+      </c>
+      <c r="F52">
+        <v>0.62</v>
+      </c>
+      <c r="G52">
+        <v>1.82</v>
+      </c>
+      <c r="H52">
+        <v>62</v>
+      </c>
+      <c r="I52">
+        <v>0.4225544208553844</v>
+      </c>
+      <c r="J52">
+        <v>381349</v>
+      </c>
+      <c r="K52">
+        <v>17202</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11">
+      <c r="A53" t="s">
+        <v>62</v>
+      </c>
+      <c r="B53">
+        <v>6</v>
+      </c>
+      <c r="C53">
+        <v>1.06</v>
+      </c>
+      <c r="D53">
+        <v>0.93</v>
+      </c>
+      <c r="E53">
+        <v>1.19</v>
+      </c>
+      <c r="F53">
+        <v>0.72</v>
+      </c>
+      <c r="G53">
+        <v>1.54</v>
+      </c>
+      <c r="H53">
+        <v>84.8</v>
+      </c>
+      <c r="I53">
+        <v>0.9482810102656085</v>
+      </c>
+      <c r="J53">
+        <v>227580</v>
+      </c>
+      <c r="K53">
+        <v>15976</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11">
+      <c r="A54" t="s">
+        <v>63</v>
+      </c>
+      <c r="B54">
+        <v>2</v>
+      </c>
+      <c r="C54">
+        <v>1.1</v>
+      </c>
+      <c r="D54">
+        <v>0.8</v>
+      </c>
+      <c r="E54">
+        <v>1.52</v>
+      </c>
+      <c r="H54">
+        <v>82.8</v>
+      </c>
+      <c r="J54">
+        <v>164504</v>
+      </c>
+      <c r="K54">
+        <v>5404</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11">
+      <c r="A55" t="s">
+        <v>64</v>
+      </c>
+      <c r="B55">
+        <v>1</v>
+      </c>
+      <c r="C55">
+        <v>1.11</v>
+      </c>
+      <c r="D55">
+        <v>1.01</v>
+      </c>
+      <c r="E55">
+        <v>1.19</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>207</v>
+      </c>
+      <c r="K55">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11">
+      <c r="A56" t="s">
+        <v>65</v>
+      </c>
+      <c r="B56">
+        <v>3</v>
+      </c>
+      <c r="C56">
+        <v>1.15</v>
+      </c>
+      <c r="D56">
+        <v>0.83</v>
+      </c>
+      <c r="E56">
+        <v>1.6</v>
+      </c>
+      <c r="F56">
+        <v>0.02</v>
+      </c>
+      <c r="G56">
+        <v>66.03</v>
+      </c>
+      <c r="H56">
+        <v>90.09999999999999</v>
+      </c>
+      <c r="I56">
+        <v>0.2027623455533696</v>
+      </c>
+      <c r="J56">
+        <v>3007</v>
+      </c>
+      <c r="K56">
+        <v>2112</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11">
+      <c r="A57" t="s">
+        <v>66</v>
+      </c>
+      <c r="B57">
+        <v>3</v>
+      </c>
+      <c r="C57">
+        <v>1.16</v>
+      </c>
+      <c r="D57">
+        <v>1.06</v>
+      </c>
+      <c r="E57">
+        <v>1.27</v>
+      </c>
+      <c r="F57">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="G57">
+        <v>2.41</v>
+      </c>
+      <c r="H57">
+        <v>9.4</v>
+      </c>
+      <c r="I57">
+        <v>0.007710468016485216</v>
+      </c>
+      <c r="J57">
+        <v>66508</v>
+      </c>
+      <c r="K57">
+        <v>1506</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11">
+      <c r="A58" t="s">
+        <v>67</v>
+      </c>
+      <c r="B58">
+        <v>13</v>
+      </c>
+      <c r="C58">
+        <v>1.16</v>
+      </c>
+      <c r="D58">
+        <v>0.73</v>
+      </c>
+      <c r="E58">
+        <v>1.84</v>
+      </c>
+      <c r="F58">
+        <v>0.18</v>
+      </c>
+      <c r="G58">
+        <v>7.55</v>
+      </c>
+      <c r="H58">
+        <v>95.8</v>
+      </c>
+      <c r="I58">
+        <v>0.521843776496502</v>
+      </c>
+      <c r="J58">
+        <v>95776</v>
+      </c>
+      <c r="K58">
+        <v>7950</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11">
+      <c r="A59" t="s">
+        <v>68</v>
+      </c>
+      <c r="B59">
+        <v>21</v>
+      </c>
+      <c r="C59">
+        <v>1.22</v>
+      </c>
+      <c r="D59">
+        <v>1.08</v>
+      </c>
+      <c r="E59">
+        <v>1.38</v>
+      </c>
+      <c r="F59">
+        <v>0.72</v>
+      </c>
+      <c r="G59">
+        <v>2.08</v>
+      </c>
+      <c r="H59">
+        <v>92.5</v>
+      </c>
+      <c r="I59">
+        <v>0.2296371298765957</v>
+      </c>
+      <c r="J59">
+        <v>1846647</v>
+      </c>
+      <c r="K59">
+        <v>65167</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11">
+      <c r="A60" t="s">
+        <v>69</v>
+      </c>
+      <c r="B60">
+        <v>1</v>
+      </c>
+      <c r="C60">
+        <v>1.24</v>
+      </c>
+      <c r="D60">
+        <v>1.05</v>
+      </c>
+      <c r="E60">
+        <v>1.47</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>2286</v>
+      </c>
+      <c r="K60">
+        <v>2286</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11">
+      <c r="A61" t="s">
+        <v>70</v>
+      </c>
+      <c r="B61">
+        <v>5</v>
+      </c>
+      <c r="C61">
+        <v>1.26</v>
+      </c>
+      <c r="D61">
+        <v>1.02</v>
+      </c>
+      <c r="E61">
+        <v>1.57</v>
+      </c>
+      <c r="F61">
+        <v>0.57</v>
+      </c>
+      <c r="G61">
+        <v>2.79</v>
+      </c>
+      <c r="H61">
+        <v>89</v>
+      </c>
+      <c r="I61">
+        <v>0.1248207118858098</v>
+      </c>
+      <c r="J61">
+        <v>384310</v>
+      </c>
+      <c r="K61">
+        <v>141179</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11">
+      <c r="A62" t="s">
+        <v>71</v>
+      </c>
+      <c r="B62">
+        <v>26</v>
+      </c>
+      <c r="C62">
+        <v>1.32</v>
+      </c>
+      <c r="D62">
+        <v>1.18</v>
+      </c>
+      <c r="E62">
+        <v>1.49</v>
+      </c>
+      <c r="F62">
+        <v>0.82</v>
+      </c>
+      <c r="G62">
+        <v>2.13</v>
+      </c>
+      <c r="H62">
+        <v>77.3</v>
+      </c>
+      <c r="I62">
+        <v>0.01965485269656792</v>
+      </c>
+      <c r="J62">
+        <v>229848</v>
+      </c>
+      <c r="K62">
+        <v>130588</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11">
+      <c r="A63" t="s">
+        <v>72</v>
+      </c>
+      <c r="B63">
+        <v>1</v>
+      </c>
+      <c r="C63">
+        <v>1.4</v>
+      </c>
+      <c r="D63">
+        <v>1.39</v>
+      </c>
+      <c r="E63">
+        <v>1.4</v>
+      </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>124896418350</v>
+      </c>
+      <c r="K63">
+        <v>51623922</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11">
+      <c r="A64" t="s">
+        <v>73</v>
+      </c>
+      <c r="B64">
+        <v>2</v>
+      </c>
+      <c r="C64">
+        <v>1.42</v>
+      </c>
+      <c r="D64">
+        <v>0.8</v>
+      </c>
+      <c r="E64">
+        <v>2.5</v>
+      </c>
+      <c r="H64">
+        <v>50.6</v>
+      </c>
+      <c r="J64">
+        <v>43940</v>
+      </c>
+      <c r="K64">
+        <v>1688</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11">
+      <c r="A65" t="s">
+        <v>74</v>
+      </c>
+      <c r="B65">
+        <v>1</v>
+      </c>
+      <c r="C65">
+        <v>1.47</v>
+      </c>
+      <c r="D65">
+        <v>1.19</v>
+      </c>
+      <c r="E65">
+        <v>1.79</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>2473</v>
+      </c>
+      <c r="K65">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11">
+      <c r="A66" t="s">
+        <v>75</v>
+      </c>
+      <c r="B66">
+        <v>1</v>
+      </c>
+      <c r="C66">
+        <v>1.55</v>
+      </c>
+      <c r="D66">
+        <v>1.06</v>
+      </c>
+      <c r="E66">
+        <v>2.23</v>
+      </c>
+      <c r="H66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>718</v>
+      </c>
+      <c r="K66">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11">
+      <c r="A67" t="s">
+        <v>76</v>
+      </c>
+      <c r="B67">
+        <v>2</v>
+      </c>
+      <c r="C67">
+        <v>1.57</v>
+      </c>
+      <c r="D67">
+        <v>0.75</v>
+      </c>
+      <c r="E67">
+        <v>3.29</v>
+      </c>
+      <c r="H67">
+        <v>82.3</v>
+      </c>
+      <c r="J67">
+        <v>1044</v>
+      </c>
+      <c r="K67">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11">
+      <c r="A68" t="s">
+        <v>77</v>
+      </c>
+      <c r="B68">
+        <v>1</v>
+      </c>
+      <c r="C68">
+        <v>1.94</v>
+      </c>
+      <c r="D68">
+        <v>1.19</v>
+      </c>
+      <c r="E68">
+        <v>2.96</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>449</v>
+      </c>
+      <c r="K68">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11">
+      <c r="A69" t="s">
+        <v>78</v>
+      </c>
+      <c r="B69">
+        <v>1</v>
+      </c>
+      <c r="C69">
+        <v>1.99</v>
+      </c>
+      <c r="D69">
+        <v>0.97</v>
+      </c>
+      <c r="E69">
+        <v>3.75</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>3069</v>
+      </c>
+      <c r="K69">
+        <v>162</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/exposures_meta_analysis_final_combined.xlsx
+++ b/exposures_meta_analysis_final_combined.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
   <si>
     <t>Exposure</t>
   </si>
@@ -97,12 +97,12 @@
     <t>folic_acid</t>
   </si>
   <si>
+    <t>resveratrol</t>
+  </si>
+  <si>
     <t>pantothenic_acid</t>
   </si>
   <si>
-    <t>resveratrol</t>
-  </si>
-  <si>
     <t>vitamin_b1</t>
   </si>
   <si>
@@ -130,36 +130,36 @@
     <t>beta-carotene</t>
   </si>
   <si>
+    <t>fermented_foods</t>
+  </si>
+  <si>
     <t>magnesium</t>
   </si>
   <si>
     <t>iodine</t>
   </si>
   <si>
+    <t>flax</t>
+  </si>
+  <si>
     <t>flaxseed</t>
   </si>
   <si>
     <t>vitamin_c</t>
   </si>
   <si>
-    <t>flax</t>
-  </si>
-  <si>
     <t>green_tea</t>
   </si>
   <si>
     <t>copper</t>
   </si>
   <si>
+    <t>calcium</t>
+  </si>
+  <si>
     <t>mushrooms</t>
   </si>
   <si>
-    <t>calcium</t>
-  </si>
-  <si>
-    <t>fermented_foods</t>
-  </si>
-  <si>
     <t>selenium</t>
   </si>
   <si>
@@ -187,12 +187,12 @@
     <t>omega-3_fatty_acids</t>
   </si>
   <si>
+    <t>caffeine</t>
+  </si>
+  <si>
     <t>leucine</t>
   </si>
   <si>
-    <t>caffeine</t>
-  </si>
-  <si>
     <t>isoleucine</t>
   </si>
   <si>
@@ -230,6 +230,9 @@
   </si>
   <si>
     <t>dehydroepiandrosterone</t>
+  </si>
+  <si>
+    <t>red_meat</t>
   </si>
   <si>
     <t>cannabidiol</t>
@@ -608,7 +611,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K69"/>
+  <dimension ref="A1:K70"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -1172,19 +1175,19 @@
         <v>0.73</v>
       </c>
       <c r="D18">
-        <v>0.53</v>
+        <v>0.59</v>
       </c>
       <c r="E18">
-        <v>0.97</v>
+        <v>0.9</v>
       </c>
       <c r="H18">
         <v>0</v>
       </c>
       <c r="J18">
-        <v>969</v>
+        <v>3049</v>
       </c>
       <c r="K18">
-        <v>453</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1198,19 +1201,19 @@
         <v>0.73</v>
       </c>
       <c r="D19">
-        <v>0.59</v>
+        <v>0.53</v>
       </c>
       <c r="E19">
-        <v>0.9</v>
+        <v>0.97</v>
       </c>
       <c r="H19">
         <v>0</v>
       </c>
       <c r="J19">
-        <v>3049</v>
+        <v>969</v>
       </c>
       <c r="K19">
-        <v>1472</v>
+        <v>453</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1515,34 +1518,34 @@
         <v>38</v>
       </c>
       <c r="B29">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C29">
         <v>0.8100000000000001</v>
       </c>
       <c r="D29">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="E29">
-        <v>0.95</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F29">
-        <v>0.46</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G29">
-        <v>1.42</v>
+        <v>1.18</v>
       </c>
       <c r="H29">
-        <v>87.09999999999999</v>
+        <v>63.9</v>
       </c>
       <c r="I29">
-        <v>0.0005795809350502423</v>
+        <v>0.0933265205349211</v>
       </c>
       <c r="J29">
-        <v>1134079</v>
+        <v>92433</v>
       </c>
       <c r="K29">
-        <v>146180</v>
+        <v>41077</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1550,34 +1553,34 @@
         <v>39</v>
       </c>
       <c r="B30">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C30">
-        <v>0.83</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="D30">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E30">
-        <v>1.39</v>
+        <v>0.95</v>
       </c>
       <c r="F30">
-        <v>0.12</v>
+        <v>0.46</v>
       </c>
       <c r="G30">
-        <v>6.05</v>
+        <v>1.42</v>
       </c>
       <c r="H30">
-        <v>98.3</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="I30">
-        <v>0.2623242622855663</v>
+        <v>0.0005795809350502423</v>
       </c>
       <c r="J30">
-        <v>261271</v>
+        <v>1134079</v>
       </c>
       <c r="K30">
-        <v>9445</v>
+        <v>146180</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1585,25 +1588,34 @@
         <v>40</v>
       </c>
       <c r="B31">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C31">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="D31">
-        <v>0.72</v>
+        <v>0.5</v>
       </c>
       <c r="E31">
-        <v>0.97</v>
+        <v>1.39</v>
+      </c>
+      <c r="F31">
+        <v>0.12</v>
+      </c>
+      <c r="G31">
+        <v>6.05</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>98.3</v>
+      </c>
+      <c r="I31">
+        <v>0.2623242622855663</v>
       </c>
       <c r="J31">
-        <v>6299</v>
+        <v>261271</v>
       </c>
       <c r="K31">
-        <v>2999</v>
+        <v>9445</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1611,34 +1623,25 @@
         <v>41</v>
       </c>
       <c r="B32">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="C32">
         <v>0.84</v>
       </c>
       <c r="D32">
-        <v>0.74</v>
+        <v>0.72</v>
       </c>
       <c r="E32">
-        <v>0.96</v>
-      </c>
-      <c r="F32">
-        <v>0.46</v>
-      </c>
-      <c r="G32">
-        <v>1.55</v>
+        <v>0.97</v>
       </c>
       <c r="H32">
-        <v>87.40000000000001</v>
-      </c>
-      <c r="I32">
-        <v>0.1658558104216727</v>
+        <v>0</v>
       </c>
       <c r="J32">
-        <v>497189</v>
+        <v>6369</v>
       </c>
       <c r="K32">
-        <v>36327</v>
+        <v>2999</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -1661,7 +1664,7 @@
         <v>0</v>
       </c>
       <c r="J33">
-        <v>6369</v>
+        <v>6299</v>
       </c>
       <c r="K33">
         <v>2999</v>
@@ -1672,34 +1675,34 @@
         <v>43</v>
       </c>
       <c r="B34">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="C34">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="D34">
-        <v>0.8100000000000001</v>
+        <v>0.74</v>
       </c>
       <c r="E34">
-        <v>0.89</v>
+        <v>0.96</v>
       </c>
       <c r="F34">
-        <v>0.67</v>
+        <v>0.46</v>
       </c>
       <c r="G34">
-        <v>1.07</v>
+        <v>1.55</v>
       </c>
       <c r="H34">
-        <v>86.90000000000001</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="I34">
-        <v>6.802984271605328E-06</v>
+        <v>0.1658558104216727</v>
       </c>
       <c r="J34">
-        <v>4809089</v>
+        <v>497189</v>
       </c>
       <c r="K34">
-        <v>311206</v>
+        <v>36327</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -1707,34 +1710,34 @@
         <v>44</v>
       </c>
       <c r="B35">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="C35">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="D35">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E35">
+        <v>0.89</v>
+      </c>
+      <c r="F35">
         <v>0.67</v>
       </c>
-      <c r="E35">
-        <v>1.09</v>
-      </c>
-      <c r="F35">
-        <v>0.38</v>
-      </c>
       <c r="G35">
-        <v>1.95</v>
+        <v>1.07</v>
       </c>
       <c r="H35">
-        <v>87</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="I35">
-        <v>0.2524762887623844</v>
+        <v>6.802984271605328E-06</v>
       </c>
       <c r="J35">
-        <v>97079</v>
+        <v>4809089</v>
       </c>
       <c r="K35">
-        <v>10555</v>
+        <v>311206</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -1742,34 +1745,34 @@
         <v>45</v>
       </c>
       <c r="B36">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C36">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
       <c r="D36">
-        <v>0.39</v>
+        <v>0.67</v>
       </c>
       <c r="E36">
-        <v>1.93</v>
+        <v>1.09</v>
       </c>
       <c r="F36">
-        <v>0.05</v>
+        <v>0.38</v>
       </c>
       <c r="G36">
-        <v>15.78</v>
+        <v>1.95</v>
       </c>
       <c r="H36">
-        <v>93.8</v>
+        <v>87</v>
       </c>
       <c r="I36">
-        <v>0.2932388285196719</v>
+        <v>0.2524762887623844</v>
       </c>
       <c r="J36">
-        <v>4444</v>
+        <v>97079</v>
       </c>
       <c r="K36">
-        <v>2146</v>
+        <v>10555</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -1812,34 +1815,34 @@
         <v>47</v>
       </c>
       <c r="B38">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C38">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="D38">
-        <v>0.77</v>
+        <v>0.39</v>
       </c>
       <c r="E38">
-        <v>1.04</v>
+        <v>1.93</v>
       </c>
       <c r="F38">
-        <v>0.6</v>
+        <v>0.05</v>
       </c>
       <c r="G38">
-        <v>1.34</v>
+        <v>15.78</v>
       </c>
       <c r="H38">
-        <v>65.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="I38">
-        <v>0.5466234157697405</v>
+        <v>0.2932388285196719</v>
       </c>
       <c r="J38">
-        <v>92433</v>
+        <v>4444</v>
       </c>
       <c r="K38">
-        <v>41077</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -2153,34 +2156,34 @@
         <v>57</v>
       </c>
       <c r="B48">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C48">
         <v>1.01</v>
       </c>
       <c r="D48">
-        <v>0.91</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E48">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="F48">
-        <v>0.65</v>
+        <v>0.78</v>
       </c>
       <c r="G48">
-        <v>1.57</v>
+        <v>1.31</v>
       </c>
       <c r="H48">
-        <v>80.8</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="I48">
-        <v>0.5613202208181793</v>
+        <v>0.6418968892061229</v>
       </c>
       <c r="J48">
-        <v>225687</v>
+        <v>650466</v>
       </c>
       <c r="K48">
-        <v>14912</v>
+        <v>35940</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -2188,34 +2191,34 @@
         <v>58</v>
       </c>
       <c r="B49">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C49">
         <v>1.01</v>
       </c>
       <c r="D49">
-        <v>0.9399999999999999</v>
+        <v>0.91</v>
       </c>
       <c r="E49">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="F49">
-        <v>0.78</v>
+        <v>0.65</v>
       </c>
       <c r="G49">
-        <v>1.31</v>
+        <v>1.57</v>
       </c>
       <c r="H49">
-        <v>81.90000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="I49">
-        <v>0.6418968892061229</v>
+        <v>0.5613202208181793</v>
       </c>
       <c r="J49">
-        <v>650466</v>
+        <v>225687</v>
       </c>
       <c r="K49">
-        <v>35940</v>
+        <v>14912</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -2651,25 +2654,34 @@
         <v>72</v>
       </c>
       <c r="B63">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="C63">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="D63">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="E63">
-        <v>1.4</v>
+        <v>1.51</v>
+      </c>
+      <c r="F63">
+        <v>0.95</v>
+      </c>
+      <c r="G63">
+        <v>2.05</v>
       </c>
       <c r="H63">
-        <v>0</v>
+        <v>88.2</v>
+      </c>
+      <c r="I63">
+        <v>2.915148377275397E-11</v>
       </c>
       <c r="J63">
-        <v>124896418350</v>
+        <v>980636</v>
       </c>
       <c r="K63">
-        <v>51623922</v>
+        <v>56842</v>
       </c>
     </row>
     <row r="64" spans="1:11">
@@ -2677,25 +2689,25 @@
         <v>73</v>
       </c>
       <c r="B64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C64">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="D64">
-        <v>0.8</v>
+        <v>1.39</v>
       </c>
       <c r="E64">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="H64">
-        <v>50.6</v>
+        <v>0</v>
       </c>
       <c r="J64">
-        <v>43940</v>
+        <v>124896418350</v>
       </c>
       <c r="K64">
-        <v>1688</v>
+        <v>51623922</v>
       </c>
     </row>
     <row r="65" spans="1:11">
@@ -2703,25 +2715,25 @@
         <v>74</v>
       </c>
       <c r="B65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C65">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="D65">
-        <v>1.19</v>
+        <v>0.8</v>
       </c>
       <c r="E65">
-        <v>1.79</v>
+        <v>2.5</v>
       </c>
       <c r="H65">
-        <v>0</v>
+        <v>50.6</v>
       </c>
       <c r="J65">
-        <v>2473</v>
+        <v>43940</v>
       </c>
       <c r="K65">
-        <v>949</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="66" spans="1:11">
@@ -2732,22 +2744,22 @@
         <v>1</v>
       </c>
       <c r="C66">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="D66">
-        <v>1.06</v>
+        <v>1.19</v>
       </c>
       <c r="E66">
-        <v>2.23</v>
+        <v>1.79</v>
       </c>
       <c r="H66">
         <v>0</v>
       </c>
       <c r="J66">
-        <v>718</v>
+        <v>2473</v>
       </c>
       <c r="K66">
-        <v>718</v>
+        <v>949</v>
       </c>
     </row>
     <row r="67" spans="1:11">
@@ -2755,25 +2767,25 @@
         <v>76</v>
       </c>
       <c r="B67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C67">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="D67">
-        <v>0.75</v>
+        <v>1.06</v>
       </c>
       <c r="E67">
-        <v>3.29</v>
+        <v>2.23</v>
       </c>
       <c r="H67">
-        <v>82.3</v>
+        <v>0</v>
       </c>
       <c r="J67">
-        <v>1044</v>
+        <v>718</v>
       </c>
       <c r="K67">
-        <v>437</v>
+        <v>718</v>
       </c>
     </row>
     <row r="68" spans="1:11">
@@ -2781,25 +2793,25 @@
         <v>77</v>
       </c>
       <c r="B68">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C68">
-        <v>1.94</v>
+        <v>1.57</v>
       </c>
       <c r="D68">
-        <v>1.19</v>
+        <v>0.75</v>
       </c>
       <c r="E68">
-        <v>2.96</v>
+        <v>3.29</v>
       </c>
       <c r="H68">
-        <v>0</v>
+        <v>82.3</v>
       </c>
       <c r="J68">
-        <v>449</v>
+        <v>1044</v>
       </c>
       <c r="K68">
-        <v>160</v>
+        <v>437</v>
       </c>
     </row>
     <row r="69" spans="1:11">
@@ -2810,21 +2822,47 @@
         <v>1</v>
       </c>
       <c r="C69">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="D69">
-        <v>0.97</v>
+        <v>1.19</v>
       </c>
       <c r="E69">
-        <v>3.75</v>
+        <v>2.96</v>
       </c>
       <c r="H69">
         <v>0</v>
       </c>
       <c r="J69">
+        <v>449</v>
+      </c>
+      <c r="K69">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11">
+      <c r="A70" t="s">
+        <v>79</v>
+      </c>
+      <c r="B70">
+        <v>1</v>
+      </c>
+      <c r="C70">
+        <v>1.99</v>
+      </c>
+      <c r="D70">
+        <v>0.97</v>
+      </c>
+      <c r="E70">
+        <v>3.75</v>
+      </c>
+      <c r="H70">
+        <v>0</v>
+      </c>
+      <c r="J70">
         <v>3069</v>
       </c>
-      <c r="K69">
+      <c r="K70">
         <v>162</v>
       </c>
     </row>

--- a/exposures_meta_analysis_final_combined.xlsx
+++ b/exposures_meta_analysis_final_combined.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="83">
   <si>
     <t>Exposure</t>
   </si>
@@ -55,175 +55,211 @@
     <t>sauerkraut</t>
   </si>
   <si>
+    <t>cesium</t>
+  </si>
+  <si>
+    <t>potassium</t>
+  </si>
+  <si>
+    <t>papaya</t>
+  </si>
+  <si>
+    <t>molybdenum</t>
+  </si>
+  <si>
     <t>vitamin_b6</t>
   </si>
   <si>
+    <t>black_cohosh</t>
+  </si>
+  <si>
+    <t>legumes</t>
+  </si>
+  <si>
+    <t>grape</t>
+  </si>
+  <si>
+    <t>lutein</t>
+  </si>
+  <si>
+    <t>omega-3_fatty_acids</t>
+  </si>
+  <si>
+    <t>vitamin_b12</t>
+  </si>
+  <si>
+    <t>iodine</t>
+  </si>
+  <si>
+    <t>lycopene</t>
+  </si>
+  <si>
+    <t>n-acetylcysteine</t>
+  </si>
+  <si>
+    <t>oats</t>
+  </si>
+  <si>
+    <t>garlic</t>
+  </si>
+  <si>
+    <t>antioxidants</t>
+  </si>
+  <si>
+    <t>mediterranean_diet</t>
+  </si>
+  <si>
+    <t>soy</t>
+  </si>
+  <si>
+    <t>vitamin_b1</t>
+  </si>
+  <si>
+    <t>olive</t>
+  </si>
+  <si>
+    <t>fish_oil</t>
+  </si>
+  <si>
+    <t>choline</t>
+  </si>
+  <si>
+    <t>mineral_supplements</t>
+  </si>
+  <si>
+    <t>betaine</t>
+  </si>
+  <si>
+    <t>cod_liver_oil</t>
+  </si>
+  <si>
+    <t>beta-carotene</t>
+  </si>
+  <si>
+    <t>miso</t>
+  </si>
+  <si>
+    <t>folic_acid</t>
+  </si>
+  <si>
+    <t>non-alcoholic_fermented_foods</t>
+  </si>
+  <si>
+    <t>flaxseed</t>
+  </si>
+  <si>
+    <t>vitamin_d</t>
+  </si>
+  <si>
+    <t>flax</t>
+  </si>
+  <si>
+    <t>fermented_foods</t>
+  </si>
+  <si>
+    <t>melatonin</t>
+  </si>
+  <si>
+    <t>manganese</t>
+  </si>
+  <si>
+    <t>yogurt</t>
+  </si>
+  <si>
+    <t>green_tea</t>
+  </si>
+  <si>
+    <t>vitamin_a</t>
+  </si>
+  <si>
+    <t>calcium</t>
+  </si>
+  <si>
+    <t>vitamin_e</t>
+  </si>
+  <si>
+    <t>vitamin_c</t>
+  </si>
+  <si>
+    <t>selenium</t>
+  </si>
+  <si>
+    <t>caffeine</t>
+  </si>
+  <si>
+    <t>bcaas</t>
+  </si>
+  <si>
+    <t>dairy</t>
+  </si>
+  <si>
+    <t>isoleucine</t>
+  </si>
+  <si>
+    <t>mushrooms</t>
+  </si>
+  <si>
+    <t>leucine</t>
+  </si>
+  <si>
+    <t>vitamin_k</t>
+  </si>
+  <si>
+    <t>tea</t>
+  </si>
+  <si>
+    <t>quercetin</t>
+  </si>
+  <si>
+    <t>conjugated_linoleic_acid</t>
+  </si>
+  <si>
+    <t>glucosamine</t>
+  </si>
+  <si>
+    <t>magnesium</t>
+  </si>
+  <si>
+    <t>grapefruit</t>
+  </si>
+  <si>
+    <t>creatine</t>
+  </si>
+  <si>
+    <t>carnitine</t>
+  </si>
+  <si>
+    <t>chromium</t>
+  </si>
+  <si>
+    <t>zinc</t>
+  </si>
+  <si>
+    <t>glutamine</t>
+  </si>
+  <si>
+    <t>eggs</t>
+  </si>
+  <si>
+    <t>iron</t>
+  </si>
+  <si>
+    <t>dehydroepiandrosterone</t>
+  </si>
+  <si>
+    <t>phosphorus</t>
+  </si>
+  <si>
+    <t>red_meat</t>
+  </si>
+  <si>
+    <t>cannabidiol</t>
+  </si>
+  <si>
     <t>copper</t>
   </si>
   <si>
-    <t>potassium</t>
-  </si>
-  <si>
-    <t>lycopene</t>
-  </si>
-  <si>
-    <t>papaya</t>
-  </si>
-  <si>
-    <t>legumes</t>
-  </si>
-  <si>
-    <t>black_cohosh</t>
-  </si>
-  <si>
-    <t>grape</t>
-  </si>
-  <si>
-    <t>vitamin_b12</t>
-  </si>
-  <si>
-    <t>zinc</t>
-  </si>
-  <si>
-    <t>lutein</t>
-  </si>
-  <si>
-    <t>omega-3_fatty_acids</t>
-  </si>
-  <si>
-    <t>oats</t>
-  </si>
-  <si>
-    <t>n-acetylcysteine</t>
-  </si>
-  <si>
-    <t>garlic</t>
-  </si>
-  <si>
-    <t>mushrooms</t>
-  </si>
-  <si>
-    <t>mediterranean_diet</t>
-  </si>
-  <si>
-    <t>fish_oil</t>
-  </si>
-  <si>
-    <t>choline</t>
-  </si>
-  <si>
-    <t>vitamin_b1</t>
-  </si>
-  <si>
-    <t>antioxidants</t>
-  </si>
-  <si>
-    <t>soy</t>
-  </si>
-  <si>
-    <t>folic_acid</t>
-  </si>
-  <si>
-    <t>leucine</t>
-  </si>
-  <si>
-    <t>isoleucine</t>
-  </si>
-  <si>
-    <t>bcaas</t>
-  </si>
-  <si>
-    <t>mineral_supplements</t>
-  </si>
-  <si>
-    <t>cod_liver_oil</t>
-  </si>
-  <si>
-    <t>beta-carotene</t>
-  </si>
-  <si>
-    <t>betaine</t>
-  </si>
-  <si>
-    <t>olive</t>
-  </si>
-  <si>
-    <t>miso</t>
-  </si>
-  <si>
-    <t>non-alcoholic_fermented_foods</t>
-  </si>
-  <si>
-    <t>flaxseed</t>
-  </si>
-  <si>
-    <t>flax</t>
-  </si>
-  <si>
-    <t>fermented_foods</t>
-  </si>
-  <si>
-    <t>vitamin_d</t>
-  </si>
-  <si>
-    <t>vitamin_e</t>
-  </si>
-  <si>
-    <t>yogurt</t>
-  </si>
-  <si>
-    <t>green_tea</t>
-  </si>
-  <si>
-    <t>vitamin_a</t>
-  </si>
-  <si>
-    <t>magnesium</t>
-  </si>
-  <si>
-    <t>calcium</t>
-  </si>
-  <si>
-    <t>vitamin_c</t>
-  </si>
-  <si>
-    <t>caffeine</t>
-  </si>
-  <si>
-    <t>dairy</t>
-  </si>
-  <si>
-    <t>vitamin_k</t>
-  </si>
-  <si>
-    <t>tea</t>
-  </si>
-  <si>
-    <t>selenium</t>
-  </si>
-  <si>
-    <t>quercetin</t>
-  </si>
-  <si>
-    <t>conjugated_linoleic_acid</t>
-  </si>
-  <si>
-    <t>glucosamine</t>
-  </si>
-  <si>
-    <t>grapefruit</t>
-  </si>
-  <si>
-    <t>eggs</t>
-  </si>
-  <si>
-    <t>iron</t>
-  </si>
-  <si>
-    <t>red_meat</t>
-  </si>
-  <si>
-    <t>phosphorus</t>
+    <t>coenzyme_q10</t>
   </si>
   <si>
     <t>pickled_vegetables</t>
@@ -584,7 +620,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K61"/>
+  <dimension ref="A1:K73"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -679,34 +715,25 @@
         <v>13</v>
       </c>
       <c r="B4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C4">
-        <v>0.4</v>
+        <v>0.53</v>
       </c>
       <c r="D4">
-        <v>0.24</v>
+        <v>0.33</v>
       </c>
       <c r="E4">
-        <v>0.67</v>
-      </c>
-      <c r="F4">
-        <v>0.05</v>
-      </c>
-      <c r="G4">
-        <v>3.57</v>
+        <v>0.84</v>
       </c>
       <c r="H4">
-        <v>73.09999999999999</v>
-      </c>
-      <c r="I4">
-        <v>0.1770583184646599</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>52399</v>
+        <v>486</v>
       </c>
       <c r="K4">
-        <v>1212</v>
+        <v>240</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -714,25 +741,25 @@
         <v>14</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="D5">
-        <v>0.34</v>
+        <v>0.3</v>
       </c>
       <c r="E5">
         <v>1.03</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>74.7</v>
       </c>
       <c r="J5">
-        <v>663</v>
+        <v>1370</v>
       </c>
       <c r="K5">
-        <v>310</v>
+        <v>587</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -740,25 +767,25 @@
         <v>15</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="D6">
-        <v>0.3</v>
+        <v>0.37</v>
       </c>
       <c r="E6">
-        <v>1.03</v>
+        <v>0.84</v>
       </c>
       <c r="H6">
-        <v>74.7</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>1370</v>
+        <v>876</v>
       </c>
       <c r="K6">
-        <v>587</v>
+        <v>438</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -766,34 +793,34 @@
         <v>16</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C7">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="D7">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="E7">
-        <v>0.84</v>
+        <v>0.96</v>
       </c>
       <c r="F7">
-        <v>0.12</v>
+        <v>0.05</v>
       </c>
       <c r="G7">
-        <v>2.59</v>
+        <v>6.78</v>
       </c>
       <c r="H7">
-        <v>88.5</v>
+        <v>94.5</v>
       </c>
       <c r="I7">
-        <v>0.09173584726167611</v>
+        <v>0.8351773861379139</v>
       </c>
       <c r="J7">
-        <v>90844</v>
+        <v>5809</v>
       </c>
       <c r="K7">
-        <v>5625</v>
+        <v>2459</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -801,25 +828,34 @@
         <v>17</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C8">
         <v>0.5600000000000001</v>
       </c>
       <c r="D8">
-        <v>0.37</v>
+        <v>0.42</v>
       </c>
       <c r="E8">
-        <v>0.84</v>
+        <v>0.76</v>
+      </c>
+      <c r="F8">
+        <v>0.22</v>
+      </c>
+      <c r="G8">
+        <v>1.43</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>72.2</v>
+      </c>
+      <c r="I8">
+        <v>0.006929997867264431</v>
       </c>
       <c r="J8">
-        <v>876</v>
+        <v>92079</v>
       </c>
       <c r="K8">
-        <v>438</v>
+        <v>3337</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -827,34 +863,25 @@
         <v>18</v>
       </c>
       <c r="B9">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C9">
         <v>0.61</v>
       </c>
       <c r="D9">
-        <v>0.5</v>
+        <v>0.34</v>
       </c>
       <c r="E9">
-        <v>0.75</v>
-      </c>
-      <c r="F9">
-        <v>0.27</v>
-      </c>
-      <c r="G9">
-        <v>1.37</v>
+        <v>1.07</v>
       </c>
       <c r="H9">
-        <v>94.09999999999999</v>
-      </c>
-      <c r="I9">
-        <v>0.001758518003460143</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="J9">
-        <v>273560</v>
+        <v>12594</v>
       </c>
       <c r="K9">
-        <v>15479</v>
+        <v>4413</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -862,25 +889,34 @@
         <v>19</v>
       </c>
       <c r="B10">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C10">
         <v>0.61</v>
       </c>
       <c r="D10">
-        <v>0.34</v>
+        <v>0.5</v>
       </c>
       <c r="E10">
-        <v>1.07</v>
+        <v>0.75</v>
+      </c>
+      <c r="F10">
+        <v>0.27</v>
+      </c>
+      <c r="G10">
+        <v>1.37</v>
       </c>
       <c r="H10">
-        <v>76.40000000000001</v>
+        <v>94.09999999999999</v>
+      </c>
+      <c r="I10">
+        <v>0.001758518003460143</v>
       </c>
       <c r="J10">
-        <v>12594</v>
+        <v>273560</v>
       </c>
       <c r="K10">
-        <v>4413</v>
+        <v>15479</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -914,34 +950,34 @@
         <v>21</v>
       </c>
       <c r="B12">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C12">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="D12">
-        <v>0.44</v>
+        <v>0.52</v>
       </c>
       <c r="E12">
-        <v>0.95</v>
+        <v>0.74</v>
       </c>
       <c r="F12">
-        <v>0.17</v>
+        <v>0.35</v>
       </c>
       <c r="G12">
-        <v>2.42</v>
+        <v>1.11</v>
       </c>
       <c r="H12">
-        <v>88.7</v>
+        <v>78.8</v>
       </c>
       <c r="I12">
-        <v>0.09471360956321116</v>
+        <v>0.0008471154848143978</v>
       </c>
       <c r="J12">
-        <v>38506</v>
+        <v>1072840</v>
       </c>
       <c r="K12">
-        <v>8006</v>
+        <v>51083</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -949,34 +985,34 @@
         <v>22</v>
       </c>
       <c r="B13">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C13">
         <v>0.65</v>
       </c>
       <c r="D13">
-        <v>0.49</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E13">
-        <v>0.88</v>
+        <v>0.76</v>
       </c>
       <c r="F13">
-        <v>0.26</v>
+        <v>0.36</v>
       </c>
       <c r="G13">
-        <v>1.61</v>
+        <v>1.17</v>
       </c>
       <c r="H13">
-        <v>54.6</v>
+        <v>68</v>
       </c>
       <c r="I13">
-        <v>0.2487315066792916</v>
+        <v>0.5929735955651932</v>
       </c>
       <c r="J13">
-        <v>43927</v>
+        <v>242088</v>
       </c>
       <c r="K13">
-        <v>7652</v>
+        <v>10615</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -984,34 +1020,34 @@
         <v>23</v>
       </c>
       <c r="B14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C14">
         <v>0.66</v>
       </c>
       <c r="D14">
-        <v>0.55</v>
+        <v>0.48</v>
       </c>
       <c r="E14">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="F14">
-        <v>0.37</v>
+        <v>0.23</v>
       </c>
       <c r="G14">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="H14">
-        <v>76.09999999999999</v>
+        <v>87.3</v>
       </c>
       <c r="I14">
-        <v>0.001205141873155635</v>
+        <v>0.02220092332067385</v>
       </c>
       <c r="J14">
-        <v>1061834</v>
+        <v>88794</v>
       </c>
       <c r="K14">
-        <v>45572</v>
+        <v>11404</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1019,34 +1055,25 @@
         <v>24</v>
       </c>
       <c r="B15">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C15">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="D15">
-        <v>0.57</v>
+        <v>0.46</v>
       </c>
       <c r="E15">
-        <v>0.8</v>
-      </c>
-      <c r="F15">
-        <v>0.39</v>
-      </c>
-      <c r="G15">
-        <v>1.16</v>
+        <v>1</v>
       </c>
       <c r="H15">
-        <v>64.5</v>
-      </c>
-      <c r="I15">
-        <v>0.4864450605937346</v>
+        <v>44.9</v>
       </c>
       <c r="J15">
-        <v>238479</v>
+        <v>3284</v>
       </c>
       <c r="K15">
-        <v>7644</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1054,25 +1081,34 @@
         <v>25</v>
       </c>
       <c r="B16">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C16">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D16">
-        <v>0.3</v>
+        <v>0.58</v>
       </c>
       <c r="E16">
-        <v>1.65</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="F16">
+        <v>0.37</v>
+      </c>
+      <c r="G16">
+        <v>1.27</v>
       </c>
       <c r="H16">
-        <v>82.3</v>
+        <v>78.7</v>
+      </c>
+      <c r="I16">
+        <v>0.06293118354996176</v>
       </c>
       <c r="J16">
-        <v>28604</v>
+        <v>370200</v>
       </c>
       <c r="K16">
-        <v>1075</v>
+        <v>136583</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1106,34 +1142,25 @@
         <v>27</v>
       </c>
       <c r="B18">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C18">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
       <c r="D18">
-        <v>0.55</v>
+        <v>0.3</v>
       </c>
       <c r="E18">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="F18">
-        <v>0.27</v>
-      </c>
-      <c r="G18">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="H18">
-        <v>44.2</v>
-      </c>
-      <c r="I18">
-        <v>0.1879066502188126</v>
+        <v>82.3</v>
       </c>
       <c r="J18">
-        <v>243855</v>
+        <v>28604</v>
       </c>
       <c r="K18">
-        <v>1388</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1144,31 +1171,31 @@
         <v>4</v>
       </c>
       <c r="C19">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="D19">
-        <v>0.28</v>
+        <v>0.55</v>
       </c>
       <c r="E19">
-        <v>1.89</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F19">
-        <v>0.01</v>
+        <v>0.27</v>
       </c>
       <c r="G19">
-        <v>67.31999999999999</v>
+        <v>1.91</v>
       </c>
       <c r="H19">
-        <v>92.8</v>
+        <v>44.2</v>
       </c>
       <c r="I19">
-        <v>0.5941659657949845</v>
+        <v>0.1879066502188126</v>
       </c>
       <c r="J19">
-        <v>3660</v>
+        <v>243855</v>
       </c>
       <c r="K19">
-        <v>1829</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1176,34 +1203,34 @@
         <v>29</v>
       </c>
       <c r="B20">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C20">
-        <v>0.74</v>
+        <v>0.72</v>
       </c>
       <c r="D20">
-        <v>0.67</v>
+        <v>0.61</v>
       </c>
       <c r="E20">
-        <v>0.8100000000000001</v>
+        <v>0.84</v>
       </c>
       <c r="F20">
-        <v>0.51</v>
+        <v>0.4</v>
       </c>
       <c r="G20">
-        <v>1.07</v>
+        <v>1.3</v>
       </c>
       <c r="H20">
-        <v>87</v>
+        <v>84.2</v>
       </c>
       <c r="I20">
-        <v>2.930546567262832E-05</v>
+        <v>0.022216274500156</v>
       </c>
       <c r="J20">
-        <v>540284</v>
+        <v>856523</v>
       </c>
       <c r="K20">
-        <v>28689</v>
+        <v>267423</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -1211,34 +1238,34 @@
         <v>30</v>
       </c>
       <c r="B21">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="C21">
         <v>0.74</v>
       </c>
       <c r="D21">
-        <v>0.49</v>
+        <v>0.67</v>
       </c>
       <c r="E21">
-        <v>1.11</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="F21">
-        <v>0.11</v>
+        <v>0.51</v>
       </c>
       <c r="G21">
-        <v>4.78</v>
+        <v>1.07</v>
       </c>
       <c r="H21">
-        <v>87.40000000000001</v>
+        <v>87</v>
       </c>
       <c r="I21">
-        <v>0.05582483881549632</v>
+        <v>2.930546567262832E-05</v>
       </c>
       <c r="J21">
-        <v>508253</v>
+        <v>540284</v>
       </c>
       <c r="K21">
-        <v>62658</v>
+        <v>28689</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -1246,34 +1273,34 @@
         <v>31</v>
       </c>
       <c r="B22">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="C22">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="D22">
-        <v>0.45</v>
+        <v>0.65</v>
       </c>
       <c r="E22">
-        <v>1.21</v>
+        <v>0.86</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>0.32</v>
       </c>
       <c r="G22">
-        <v>361.92</v>
+        <v>1.74</v>
       </c>
       <c r="H22">
-        <v>93.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="I22">
-        <v>0.1609207366482929</v>
+        <v>0.01919136648399242</v>
       </c>
       <c r="J22">
-        <v>79262</v>
+        <v>984463</v>
       </c>
       <c r="K22">
-        <v>6305</v>
+        <v>44792</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -1307,34 +1334,34 @@
         <v>33</v>
       </c>
       <c r="B24">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C24">
         <v>0.75</v>
       </c>
       <c r="D24">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="E24">
-        <v>0.95</v>
+        <v>0.87</v>
       </c>
       <c r="F24">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
       <c r="G24">
-        <v>1.63</v>
+        <v>1.24</v>
       </c>
       <c r="H24">
-        <v>86.09999999999999</v>
+        <v>84.8</v>
       </c>
       <c r="I24">
-        <v>0.1077633081102809</v>
+        <v>0.005850985088450081</v>
       </c>
       <c r="J24">
-        <v>393342</v>
+        <v>249237</v>
       </c>
       <c r="K24">
-        <v>19057</v>
+        <v>17161</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -1342,34 +1369,34 @@
         <v>34</v>
       </c>
       <c r="B25">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="C25">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="D25">
-        <v>0.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E25">
-        <v>0.87</v>
+        <v>1.02</v>
       </c>
       <c r="F25">
-        <v>0.32</v>
+        <v>0.28</v>
       </c>
       <c r="G25">
-        <v>1.75</v>
+        <v>2.06</v>
       </c>
       <c r="H25">
-        <v>90.90000000000001</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="I25">
-        <v>0.02688524395045291</v>
+        <v>0.02000889385459846</v>
       </c>
       <c r="J25">
-        <v>943039</v>
+        <v>508427</v>
       </c>
       <c r="K25">
-        <v>43224</v>
+        <v>63225</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -1377,34 +1404,34 @@
         <v>35</v>
       </c>
       <c r="B26">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="C26">
         <v>0.76</v>
       </c>
       <c r="D26">
-        <v>0.67</v>
+        <v>0.52</v>
       </c>
       <c r="E26">
-        <v>0.85</v>
+        <v>1.11</v>
       </c>
       <c r="F26">
-        <v>0.42</v>
+        <v>0.13</v>
       </c>
       <c r="G26">
-        <v>1.36</v>
+        <v>4.41</v>
       </c>
       <c r="H26">
-        <v>85.5</v>
+        <v>90.5</v>
       </c>
       <c r="I26">
-        <v>0.002326013428354479</v>
+        <v>0.1085966579317357</v>
       </c>
       <c r="J26">
-        <v>990582</v>
+        <v>80262</v>
       </c>
       <c r="K26">
-        <v>46686</v>
+        <v>6805</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -1418,19 +1445,19 @@
         <v>0.77</v>
       </c>
       <c r="D27">
-        <v>0.4</v>
+        <v>0.63</v>
       </c>
       <c r="E27">
-        <v>1.48</v>
+        <v>0.95</v>
       </c>
       <c r="H27">
-        <v>92.8</v>
+        <v>0</v>
       </c>
       <c r="J27">
-        <v>197211</v>
+        <v>7408</v>
       </c>
       <c r="K27">
-        <v>10396</v>
+        <v>3413</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -1438,25 +1465,34 @@
         <v>37</v>
       </c>
       <c r="B28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C28">
         <v>0.77</v>
       </c>
       <c r="D28">
-        <v>0.4</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E28">
-        <v>1.48</v>
+        <v>1.07</v>
+      </c>
+      <c r="F28">
+        <v>0.02</v>
+      </c>
+      <c r="G28">
+        <v>37.25</v>
       </c>
       <c r="H28">
-        <v>92.8</v>
+        <v>81.90000000000001</v>
+      </c>
+      <c r="I28">
+        <v>0.177930339763042</v>
       </c>
       <c r="J28">
-        <v>197211</v>
+        <v>77198</v>
       </c>
       <c r="K28">
-        <v>10396</v>
+        <v>5297</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -1467,22 +1503,22 @@
         <v>2</v>
       </c>
       <c r="C29">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="D29">
-        <v>0.4</v>
+        <v>0.68</v>
       </c>
       <c r="E29">
-        <v>1.48</v>
+        <v>0.9</v>
       </c>
       <c r="H29">
-        <v>92.8</v>
+        <v>0</v>
       </c>
       <c r="J29">
-        <v>197211</v>
+        <v>4001</v>
       </c>
       <c r="K29">
-        <v>10396</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1490,25 +1526,34 @@
         <v>39</v>
       </c>
       <c r="B30">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="C30">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="D30">
-        <v>0.63</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E30">
-        <v>0.95</v>
+        <v>0.87</v>
+      </c>
+      <c r="F30">
+        <v>0.43</v>
+      </c>
+      <c r="G30">
+        <v>1.42</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>88.59999999999999</v>
+      </c>
+      <c r="I30">
+        <v>0.07736391593656719</v>
       </c>
       <c r="J30">
-        <v>7408</v>
+        <v>1733105</v>
       </c>
       <c r="K30">
-        <v>3413</v>
+        <v>124722</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1516,25 +1561,34 @@
         <v>40</v>
       </c>
       <c r="B31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C31">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="D31">
-        <v>0.68</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E31">
-        <v>0.9</v>
+        <v>1.13</v>
+      </c>
+      <c r="F31">
+        <v>0.02</v>
+      </c>
+      <c r="G31">
+        <v>33.61</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>57</v>
+      </c>
+      <c r="I31">
+        <v>0.5607534123225345</v>
       </c>
       <c r="J31">
-        <v>4001</v>
+        <v>87065</v>
       </c>
       <c r="K31">
-        <v>1731</v>
+        <v>751</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1542,34 +1596,34 @@
         <v>41</v>
       </c>
       <c r="B32">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="C32">
-        <v>0.79</v>
+        <v>0.82</v>
       </c>
       <c r="D32">
-        <v>0.7</v>
+        <v>0.74</v>
       </c>
       <c r="E32">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
       <c r="F32">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="G32">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="H32">
-        <v>89.59999999999999</v>
+        <v>84.5</v>
       </c>
       <c r="I32">
-        <v>0.1405222253858071</v>
+        <v>0.02877266109333387</v>
       </c>
       <c r="J32">
-        <v>1684061</v>
+        <v>1079462</v>
       </c>
       <c r="K32">
-        <v>114896</v>
+        <v>52354</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -1577,25 +1631,34 @@
         <v>42</v>
       </c>
       <c r="B33">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C33">
-        <v>0.79</v>
+        <v>0.83</v>
       </c>
       <c r="D33">
-        <v>0.5</v>
+        <v>0.64</v>
       </c>
       <c r="E33">
-        <v>1.25</v>
+        <v>1.07</v>
+      </c>
+      <c r="F33">
+        <v>0.35</v>
+      </c>
+      <c r="G33">
+        <v>1.98</v>
       </c>
       <c r="H33">
-        <v>88.40000000000001</v>
+        <v>91.40000000000001</v>
+      </c>
+      <c r="I33">
+        <v>0.6522742230222329</v>
       </c>
       <c r="J33">
-        <v>76198</v>
+        <v>143000</v>
       </c>
       <c r="K33">
-        <v>4797</v>
+        <v>41773</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -1603,34 +1666,25 @@
         <v>43</v>
       </c>
       <c r="B34">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C34">
-        <v>0.8</v>
+        <v>0.84</v>
       </c>
       <c r="D34">
-        <v>0.6899999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="E34">
-        <v>0.92</v>
-      </c>
-      <c r="F34">
-        <v>0.51</v>
-      </c>
-      <c r="G34">
-        <v>1.24</v>
+        <v>0.97</v>
       </c>
       <c r="H34">
-        <v>81</v>
-      </c>
-      <c r="I34">
-        <v>0.01389915282783272</v>
+        <v>0</v>
       </c>
       <c r="J34">
-        <v>248595</v>
+        <v>6369</v>
       </c>
       <c r="K34">
-        <v>16870</v>
+        <v>2999</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -1638,34 +1692,34 @@
         <v>44</v>
       </c>
       <c r="B35">
-        <v>3</v>
+        <v>81</v>
       </c>
       <c r="C35">
+        <v>0.84</v>
+      </c>
+      <c r="D35">
         <v>0.8</v>
       </c>
-      <c r="D35">
-        <v>0.5600000000000001</v>
-      </c>
       <c r="E35">
-        <v>1.13</v>
+        <v>0.87</v>
       </c>
       <c r="F35">
-        <v>0.02</v>
+        <v>0.64</v>
       </c>
       <c r="G35">
-        <v>33.61</v>
+        <v>1.1</v>
       </c>
       <c r="H35">
-        <v>57</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="I35">
-        <v>0.5607534123225345</v>
+        <v>1.08040557961013E-09</v>
       </c>
       <c r="J35">
-        <v>87065</v>
+        <v>1598193</v>
       </c>
       <c r="K35">
-        <v>751</v>
+        <v>241407</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -1673,34 +1727,25 @@
         <v>45</v>
       </c>
       <c r="B36">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C36">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="D36">
-        <v>0.64</v>
+        <v>0.72</v>
       </c>
       <c r="E36">
-        <v>1.07</v>
-      </c>
-      <c r="F36">
-        <v>0.35</v>
-      </c>
-      <c r="G36">
-        <v>1.98</v>
+        <v>0.97</v>
       </c>
       <c r="H36">
-        <v>91.40000000000001</v>
-      </c>
-      <c r="I36">
-        <v>0.6522742230222329</v>
+        <v>0</v>
       </c>
       <c r="J36">
-        <v>143000</v>
+        <v>6369</v>
       </c>
       <c r="K36">
-        <v>41773</v>
+        <v>2999</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -1708,25 +1753,34 @@
         <v>46</v>
       </c>
       <c r="B37">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C37">
         <v>0.84</v>
       </c>
       <c r="D37">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="E37">
-        <v>0.97</v>
+        <v>0.93</v>
+      </c>
+      <c r="F37">
+        <v>0.63</v>
+      </c>
+      <c r="G37">
+        <v>1.1</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>61.9</v>
+      </c>
+      <c r="I37">
+        <v>0.0063382621997759</v>
       </c>
       <c r="J37">
-        <v>6369</v>
+        <v>1687421</v>
       </c>
       <c r="K37">
-        <v>2999</v>
+        <v>248942</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -1734,25 +1788,34 @@
         <v>47</v>
       </c>
       <c r="B38">
+        <v>10</v>
+      </c>
+      <c r="C38">
+        <v>0.85</v>
+      </c>
+      <c r="D38">
+        <v>0.73</v>
+      </c>
+      <c r="E38">
         <v>1</v>
       </c>
-      <c r="C38">
-        <v>0.84</v>
-      </c>
-      <c r="D38">
-        <v>0.72</v>
-      </c>
-      <c r="E38">
-        <v>0.97</v>
+      <c r="F38">
+        <v>0.55</v>
+      </c>
+      <c r="G38">
+        <v>1.31</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>42.3</v>
+      </c>
+      <c r="I38">
+        <v>0.9864318175325137</v>
       </c>
       <c r="J38">
-        <v>6369</v>
+        <v>62422</v>
       </c>
       <c r="K38">
-        <v>2999</v>
+        <v>3175</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -1760,34 +1823,25 @@
         <v>48</v>
       </c>
       <c r="B39">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C39">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="D39">
-        <v>0.75</v>
+        <v>0.73</v>
       </c>
       <c r="E39">
-        <v>0.93</v>
-      </c>
-      <c r="F39">
-        <v>0.63</v>
-      </c>
-      <c r="G39">
-        <v>1.1</v>
+        <v>0.99</v>
       </c>
       <c r="H39">
-        <v>61.9</v>
-      </c>
-      <c r="I39">
-        <v>0.0063382621997759</v>
+        <v>0</v>
       </c>
       <c r="J39">
-        <v>1687421</v>
+        <v>2939</v>
       </c>
       <c r="K39">
-        <v>248942</v>
+        <v>382</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -1795,34 +1849,34 @@
         <v>49</v>
       </c>
       <c r="B40">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="C40">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="D40">
         <v>0.79</v>
       </c>
       <c r="E40">
-        <v>0.91</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F40">
-        <v>0.62</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G40">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="H40">
-        <v>77.2</v>
+        <v>50.4</v>
       </c>
       <c r="I40">
-        <v>0.0003895055604768785</v>
+        <v>0.01216014445622597</v>
       </c>
       <c r="J40">
-        <v>1078797</v>
+        <v>1587902</v>
       </c>
       <c r="K40">
-        <v>56579</v>
+        <v>244079</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -1830,34 +1884,34 @@
         <v>50</v>
       </c>
       <c r="B41">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C41">
         <v>0.86</v>
       </c>
       <c r="D41">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="E41">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="F41">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="G41">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="H41">
-        <v>69.7</v>
+        <v>86.8</v>
       </c>
       <c r="I41">
-        <v>0.04857888797324741</v>
+        <v>0.1084868192939508</v>
       </c>
       <c r="J41">
-        <v>265174</v>
+        <v>276424</v>
       </c>
       <c r="K41">
-        <v>29422</v>
+        <v>19220</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -1865,34 +1919,34 @@
         <v>51</v>
       </c>
       <c r="B42">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C42">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="D42">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="E42">
-        <v>0.9399999999999999</v>
+        <v>1.08</v>
       </c>
       <c r="F42">
-        <v>0.6899999999999999</v>
+        <v>0.46</v>
       </c>
       <c r="G42">
-        <v>1.08</v>
+        <v>1.8</v>
       </c>
       <c r="H42">
-        <v>50.4</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="I42">
-        <v>0.01216014445622597</v>
+        <v>0.4889561242721966</v>
       </c>
       <c r="J42">
-        <v>1587902</v>
+        <v>580493</v>
       </c>
       <c r="K42">
-        <v>244079</v>
+        <v>144042</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -1900,34 +1954,34 @@
         <v>52</v>
       </c>
       <c r="B43">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C43">
-        <v>0.86</v>
+        <v>0.92</v>
       </c>
       <c r="D43">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="E43">
-        <v>0.99</v>
+        <v>0.96</v>
       </c>
       <c r="F43">
-        <v>0.53</v>
+        <v>0.8</v>
       </c>
       <c r="G43">
-        <v>1.38</v>
+        <v>1.07</v>
       </c>
       <c r="H43">
-        <v>87.7</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="I43">
-        <v>0.11467328035644</v>
+        <v>0.004626575242725505</v>
       </c>
       <c r="J43">
-        <v>252198</v>
+        <v>930114</v>
       </c>
       <c r="K43">
-        <v>19076</v>
+        <v>77262</v>
       </c>
     </row>
     <row r="44" spans="1:11">
@@ -1935,34 +1989,34 @@
         <v>53</v>
       </c>
       <c r="B44">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C44">
-        <v>0.9</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="D44">
-        <v>0.6899999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E44">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="F44">
-        <v>0.36</v>
+        <v>0.5</v>
       </c>
       <c r="G44">
-        <v>2.26</v>
+        <v>1.74</v>
       </c>
       <c r="H44">
-        <v>89.90000000000001</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="I44">
-        <v>0.4428609557180628</v>
+        <v>0.9597674472320056</v>
       </c>
       <c r="J44">
-        <v>316681</v>
+        <v>746495</v>
       </c>
       <c r="K44">
-        <v>16741</v>
+        <v>277405</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -1970,25 +2024,34 @@
         <v>54</v>
       </c>
       <c r="B45">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C45">
-        <v>0.91</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="D45">
-        <v>0.79</v>
+        <v>0.82</v>
       </c>
       <c r="E45">
         <v>1.06</v>
       </c>
+      <c r="F45">
+        <v>0.59</v>
+      </c>
+      <c r="G45">
+        <v>1.48</v>
+      </c>
       <c r="H45">
-        <v>62.4</v>
+        <v>83</v>
+      </c>
+      <c r="I45">
+        <v>0.5612991451474085</v>
       </c>
       <c r="J45">
-        <v>69324</v>
+        <v>512782</v>
       </c>
       <c r="K45">
-        <v>9766</v>
+        <v>35415</v>
       </c>
     </row>
     <row r="46" spans="1:11">
@@ -1996,34 +2059,34 @@
         <v>55</v>
       </c>
       <c r="B46">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C46">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="D46">
-        <v>0.89</v>
+        <v>0.88</v>
       </c>
       <c r="E46">
-        <v>0.96</v>
+        <v>1.03</v>
       </c>
       <c r="F46">
-        <v>0.8100000000000001</v>
+        <v>0.74</v>
       </c>
       <c r="G46">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="H46">
-        <v>76.7</v>
+        <v>58.4</v>
       </c>
       <c r="I46">
-        <v>0.0007963767795179974</v>
+        <v>0.8524602198215492</v>
       </c>
       <c r="J46">
-        <v>908120</v>
+        <v>346098</v>
       </c>
       <c r="K46">
-        <v>75193</v>
+        <v>21359</v>
       </c>
     </row>
     <row r="47" spans="1:11">
@@ -2031,34 +2094,34 @@
         <v>56</v>
       </c>
       <c r="B47">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C47">
-        <v>0.9399999999999999</v>
+        <v>0.97</v>
       </c>
       <c r="D47">
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
       <c r="E47">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="F47">
-        <v>0.59</v>
+        <v>0.85</v>
       </c>
       <c r="G47">
-        <v>1.48</v>
+        <v>1.1</v>
       </c>
       <c r="H47">
-        <v>83</v>
+        <v>45.9</v>
       </c>
       <c r="I47">
-        <v>0.5612991451474085</v>
+        <v>0.4259906328747258</v>
       </c>
       <c r="J47">
-        <v>512782</v>
+        <v>872194</v>
       </c>
       <c r="K47">
-        <v>35415</v>
+        <v>38461</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -2066,34 +2129,34 @@
         <v>57</v>
       </c>
       <c r="B48">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C48">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="D48">
-        <v>0.92</v>
+        <v>0.87</v>
       </c>
       <c r="E48">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="F48">
-        <v>0.85</v>
+        <v>0.25</v>
       </c>
       <c r="G48">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
       <c r="H48">
-        <v>45.9</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="I48">
-        <v>0.4259906328747258</v>
+        <v>0.2941582730123408</v>
       </c>
       <c r="J48">
-        <v>872194</v>
+        <v>223922</v>
       </c>
       <c r="K48">
-        <v>38461</v>
+        <v>13868</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -2101,34 +2164,34 @@
         <v>58</v>
       </c>
       <c r="B49">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C49">
         <v>1</v>
       </c>
       <c r="D49">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="E49">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="F49">
-        <v>0.88</v>
+        <v>0.91</v>
       </c>
       <c r="G49">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="H49">
-        <v>88.5</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I49">
-        <v>0.4607632495398346</v>
+        <v>0.6133032909092402</v>
       </c>
       <c r="J49">
-        <v>4267850</v>
+        <v>4496801</v>
       </c>
       <c r="K49">
-        <v>375682</v>
+        <v>406240</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -2136,25 +2199,34 @@
         <v>59</v>
       </c>
       <c r="B50">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C50">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="D50">
-        <v>0.68</v>
+        <v>0.87</v>
       </c>
       <c r="E50">
-        <v>1.5</v>
+        <v>1.14</v>
+      </c>
+      <c r="F50">
+        <v>0.57</v>
+      </c>
+      <c r="G50">
+        <v>1.74</v>
       </c>
       <c r="H50">
-        <v>91.8</v>
+        <v>86.09999999999999</v>
+      </c>
+      <c r="I50">
+        <v>0.9376775415524358</v>
       </c>
       <c r="J50">
-        <v>5048</v>
+        <v>227916</v>
       </c>
       <c r="K50">
-        <v>2592</v>
+        <v>15865</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -2162,34 +2234,34 @@
         <v>60</v>
       </c>
       <c r="B51">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="C51">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="D51">
-        <v>0.9399999999999999</v>
+        <v>0.37</v>
       </c>
       <c r="E51">
-        <v>1.09</v>
+        <v>2.72</v>
       </c>
       <c r="F51">
-        <v>0.73</v>
+        <v>0.02</v>
       </c>
       <c r="G51">
-        <v>1.4</v>
+        <v>47.08</v>
       </c>
       <c r="H51">
-        <v>91.09999999999999</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="I51">
-        <v>0.9414296275713543</v>
+        <v>0.4031875572497586</v>
       </c>
       <c r="J51">
-        <v>1633262</v>
+        <v>4428</v>
       </c>
       <c r="K51">
-        <v>202447</v>
+        <v>1957</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -2197,34 +2269,34 @@
         <v>61</v>
       </c>
       <c r="B52">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C52">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="D52">
-        <v>0.87</v>
+        <v>0.91</v>
       </c>
       <c r="E52">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="F52">
         <v>0.65</v>
       </c>
       <c r="G52">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="H52">
-        <v>65</v>
+        <v>80.8</v>
       </c>
       <c r="I52">
-        <v>0.7255960351225049</v>
+        <v>0.5613202208181793</v>
       </c>
       <c r="J52">
-        <v>175826</v>
+        <v>225687</v>
       </c>
       <c r="K52">
-        <v>12809</v>
+        <v>15633</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -2232,25 +2304,25 @@
         <v>62</v>
       </c>
       <c r="B53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C53">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="D53">
-        <v>0.83</v>
+        <v>0.68</v>
       </c>
       <c r="E53">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="H53">
-        <v>0</v>
+        <v>91.8</v>
       </c>
       <c r="J53">
-        <v>90630</v>
+        <v>5048</v>
       </c>
       <c r="K53">
-        <v>710</v>
+        <v>2592</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -2258,34 +2330,34 @@
         <v>63</v>
       </c>
       <c r="B54">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="C54">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="D54">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="E54">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="F54">
-        <v>0.62</v>
+        <v>0.89</v>
       </c>
       <c r="G54">
-        <v>1.82</v>
+        <v>1.18</v>
       </c>
       <c r="H54">
-        <v>62</v>
+        <v>90.5</v>
       </c>
       <c r="I54">
-        <v>0.4225544208553844</v>
+        <v>0.9812909136692176</v>
       </c>
       <c r="J54">
-        <v>380443</v>
+        <v>1887493</v>
       </c>
       <c r="K54">
-        <v>17329</v>
+        <v>232708</v>
       </c>
     </row>
     <row r="55" spans="1:11">
@@ -2296,22 +2368,22 @@
         <v>1</v>
       </c>
       <c r="C55">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="D55">
-        <v>0.93</v>
+        <v>0.83</v>
       </c>
       <c r="E55">
-        <v>1.21</v>
+        <v>1.34</v>
       </c>
       <c r="H55">
         <v>0</v>
       </c>
       <c r="J55">
-        <v>41082</v>
+        <v>90630</v>
       </c>
       <c r="K55">
-        <v>5341</v>
+        <v>710</v>
       </c>
     </row>
     <row r="56" spans="1:11">
@@ -2319,25 +2391,34 @@
         <v>65</v>
       </c>
       <c r="B56">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C56">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="D56">
-        <v>0.8</v>
+        <v>0.92</v>
       </c>
       <c r="E56">
-        <v>1.52</v>
+        <v>1.22</v>
+      </c>
+      <c r="F56">
+        <v>0.62</v>
+      </c>
+      <c r="G56">
+        <v>1.82</v>
       </c>
       <c r="H56">
-        <v>82.8</v>
+        <v>62</v>
+      </c>
+      <c r="I56">
+        <v>0.4225544208553844</v>
       </c>
       <c r="J56">
-        <v>164504</v>
+        <v>380443</v>
       </c>
       <c r="K56">
-        <v>5404</v>
+        <v>17329</v>
       </c>
     </row>
     <row r="57" spans="1:11">
@@ -2345,34 +2426,25 @@
         <v>66</v>
       </c>
       <c r="B57">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C57">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="D57">
-        <v>0.95</v>
+        <v>0.93</v>
       </c>
       <c r="E57">
-        <v>1.39</v>
-      </c>
-      <c r="F57">
-        <v>0.67</v>
-      </c>
-      <c r="G57">
-        <v>1.96</v>
+        <v>1.21</v>
       </c>
       <c r="H57">
-        <v>86.59999999999999</v>
-      </c>
-      <c r="I57">
-        <v>0.7478766568479689</v>
+        <v>0</v>
       </c>
       <c r="J57">
-        <v>29487</v>
+        <v>41082</v>
       </c>
       <c r="K57">
-        <v>5481</v>
+        <v>5341</v>
       </c>
     </row>
     <row r="58" spans="1:11">
@@ -2380,34 +2452,34 @@
         <v>67</v>
       </c>
       <c r="B58">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C58">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="D58">
-        <v>1.04</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E58">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="F58">
-        <v>0.74</v>
+        <v>0.66</v>
       </c>
       <c r="G58">
-        <v>2.01</v>
+        <v>1.78</v>
       </c>
       <c r="H58">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="I58">
-        <v>0.533827914910584</v>
+        <v>0.4685196145888209</v>
       </c>
       <c r="J58">
-        <v>385425</v>
+        <v>1239364</v>
       </c>
       <c r="K58">
-        <v>22415</v>
+        <v>266355</v>
       </c>
     </row>
     <row r="59" spans="1:11">
@@ -2415,34 +2487,25 @@
         <v>68</v>
       </c>
       <c r="B59">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="C59">
-        <v>1.33</v>
+        <v>1.1</v>
       </c>
       <c r="D59">
-        <v>1.24</v>
+        <v>0.8</v>
       </c>
       <c r="E59">
-        <v>1.42</v>
-      </c>
-      <c r="F59">
-        <v>0.95</v>
-      </c>
-      <c r="G59">
-        <v>1.85</v>
+        <v>1.52</v>
       </c>
       <c r="H59">
-        <v>86.5</v>
-      </c>
-      <c r="I59">
-        <v>4.523365894739185E-11</v>
+        <v>82.8</v>
       </c>
       <c r="J59">
-        <v>1178141</v>
+        <v>164504</v>
       </c>
       <c r="K59">
-        <v>60075</v>
+        <v>5404</v>
       </c>
     </row>
     <row r="60" spans="1:11">
@@ -2453,22 +2516,22 @@
         <v>1</v>
       </c>
       <c r="C60">
-        <v>2.3</v>
+        <v>1.11</v>
       </c>
       <c r="D60">
-        <v>0.9399999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="E60">
-        <v>5.61</v>
+        <v>1.19</v>
       </c>
       <c r="H60">
         <v>0</v>
       </c>
       <c r="J60">
-        <v>370</v>
+        <v>207</v>
       </c>
       <c r="K60">
-        <v>74</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="61" spans="1:11">
@@ -2476,24 +2539,417 @@
         <v>70</v>
       </c>
       <c r="B61">
+        <v>4</v>
+      </c>
+      <c r="C61">
+        <v>1.13</v>
+      </c>
+      <c r="D61">
+        <v>0.9</v>
+      </c>
+      <c r="E61">
+        <v>1.41</v>
+      </c>
+      <c r="F61">
+        <v>0.42</v>
+      </c>
+      <c r="G61">
+        <v>3.02</v>
+      </c>
+      <c r="H61">
+        <v>82.8</v>
+      </c>
+      <c r="I61">
+        <v>0.7636681889414908</v>
+      </c>
+      <c r="J61">
+        <v>384266</v>
+      </c>
+      <c r="K61">
+        <v>140082</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11">
+      <c r="A62" t="s">
+        <v>71</v>
+      </c>
+      <c r="B62">
+        <v>3</v>
+      </c>
+      <c r="C62">
+        <v>1.13</v>
+      </c>
+      <c r="D62">
+        <v>1.06</v>
+      </c>
+      <c r="E62">
+        <v>1.21</v>
+      </c>
+      <c r="F62">
+        <v>0.74</v>
+      </c>
+      <c r="G62">
+        <v>1.74</v>
+      </c>
+      <c r="H62">
+        <v>0</v>
+      </c>
+      <c r="I62">
+        <v>0.987786419099957</v>
+      </c>
+      <c r="J62">
+        <v>66508</v>
+      </c>
+      <c r="K62">
+        <v>1506</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11">
+      <c r="A63" t="s">
+        <v>72</v>
+      </c>
+      <c r="B63">
+        <v>10</v>
+      </c>
+      <c r="C63">
+        <v>1.14</v>
+      </c>
+      <c r="D63">
+        <v>0.68</v>
+      </c>
+      <c r="E63">
+        <v>1.91</v>
+      </c>
+      <c r="F63">
+        <v>0.16</v>
+      </c>
+      <c r="G63">
+        <v>8.09</v>
+      </c>
+      <c r="H63">
+        <v>96</v>
+      </c>
+      <c r="I63">
+        <v>0.6073544042976851</v>
+      </c>
+      <c r="J63">
+        <v>119440</v>
+      </c>
+      <c r="K63">
+        <v>10103</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11">
+      <c r="A64" t="s">
+        <v>73</v>
+      </c>
+      <c r="B64">
+        <v>3</v>
+      </c>
+      <c r="C64">
+        <v>1.14</v>
+      </c>
+      <c r="D64">
+        <v>0.8</v>
+      </c>
+      <c r="E64">
+        <v>1.63</v>
+      </c>
+      <c r="F64">
+        <v>0.01</v>
+      </c>
+      <c r="G64">
+        <v>93.62</v>
+      </c>
+      <c r="H64">
+        <v>91.5</v>
+      </c>
+      <c r="I64">
+        <v>0.214434325667662</v>
+      </c>
+      <c r="J64">
+        <v>4702</v>
+      </c>
+      <c r="K64">
+        <v>2112</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11">
+      <c r="A65" t="s">
+        <v>74</v>
+      </c>
+      <c r="B65">
+        <v>9</v>
+      </c>
+      <c r="C65">
+        <v>1.15</v>
+      </c>
+      <c r="D65">
+        <v>0.95</v>
+      </c>
+      <c r="E65">
+        <v>1.39</v>
+      </c>
+      <c r="F65">
+        <v>0.67</v>
+      </c>
+      <c r="G65">
+        <v>1.96</v>
+      </c>
+      <c r="H65">
+        <v>86.59999999999999</v>
+      </c>
+      <c r="I65">
+        <v>0.7478766568479689</v>
+      </c>
+      <c r="J65">
+        <v>29487</v>
+      </c>
+      <c r="K65">
+        <v>5481</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11">
+      <c r="A66" t="s">
+        <v>75</v>
+      </c>
+      <c r="B66">
+        <v>21</v>
+      </c>
+      <c r="C66">
+        <v>1.16</v>
+      </c>
+      <c r="D66">
+        <v>1.07</v>
+      </c>
+      <c r="E66">
+        <v>1.26</v>
+      </c>
+      <c r="F66">
+        <v>0.84</v>
+      </c>
+      <c r="G66">
+        <v>1.6</v>
+      </c>
+      <c r="H66">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="I66">
+        <v>0.1103508883242969</v>
+      </c>
+      <c r="J66">
+        <v>1380324</v>
+      </c>
+      <c r="K66">
+        <v>223058</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11">
+      <c r="A67" t="s">
+        <v>76</v>
+      </c>
+      <c r="B67">
+        <v>15</v>
+      </c>
+      <c r="C67">
+        <v>1.25</v>
+      </c>
+      <c r="D67">
+        <v>1.15</v>
+      </c>
+      <c r="E67">
+        <v>1.36</v>
+      </c>
+      <c r="F67">
+        <v>0.97</v>
+      </c>
+      <c r="G67">
+        <v>1.61</v>
+      </c>
+      <c r="H67">
+        <v>62.7</v>
+      </c>
+      <c r="I67">
+        <v>6.586804402476452E-05</v>
+      </c>
+      <c r="J67">
+        <v>249396</v>
+      </c>
+      <c r="K67">
+        <v>127523</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11">
+      <c r="A68" t="s">
+        <v>77</v>
+      </c>
+      <c r="B68">
+        <v>2</v>
+      </c>
+      <c r="C68">
+        <v>1.27</v>
+      </c>
+      <c r="D68">
+        <v>0.49</v>
+      </c>
+      <c r="E68">
+        <v>3.26</v>
+      </c>
+      <c r="H68">
+        <v>78.2</v>
+      </c>
+      <c r="J68">
+        <v>229321</v>
+      </c>
+      <c r="K68">
+        <v>123051</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11">
+      <c r="A69" t="s">
+        <v>78</v>
+      </c>
+      <c r="B69">
+        <v>35</v>
+      </c>
+      <c r="C69">
+        <v>1.27</v>
+      </c>
+      <c r="D69">
+        <v>1.2</v>
+      </c>
+      <c r="E69">
+        <v>1.34</v>
+      </c>
+      <c r="F69">
         <v>1</v>
       </c>
-      <c r="C61">
+      <c r="G69">
+        <v>1.61</v>
+      </c>
+      <c r="H69">
+        <v>88.3</v>
+      </c>
+      <c r="I69">
+        <v>1.319761565701656E-10</v>
+      </c>
+      <c r="J69">
+        <v>1260095</v>
+      </c>
+      <c r="K69">
+        <v>70729</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11">
+      <c r="A70" t="s">
+        <v>79</v>
+      </c>
+      <c r="B70">
+        <v>1</v>
+      </c>
+      <c r="C70">
+        <v>1.4</v>
+      </c>
+      <c r="D70">
+        <v>1.39</v>
+      </c>
+      <c r="E70">
+        <v>1.4</v>
+      </c>
+      <c r="H70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>124896418350</v>
+      </c>
+      <c r="K70">
+        <v>51623922</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11">
+      <c r="A71" t="s">
+        <v>80</v>
+      </c>
+      <c r="B71">
+        <v>7</v>
+      </c>
+      <c r="C71">
+        <v>1.66</v>
+      </c>
+      <c r="D71">
+        <v>1.07</v>
+      </c>
+      <c r="E71">
+        <v>2.56</v>
+      </c>
+      <c r="F71">
+        <v>0.37</v>
+      </c>
+      <c r="G71">
+        <v>7.5</v>
+      </c>
+      <c r="H71">
+        <v>89</v>
+      </c>
+      <c r="I71">
+        <v>0.4612984675749358</v>
+      </c>
+      <c r="J71">
+        <v>65747</v>
+      </c>
+      <c r="K71">
+        <v>1930</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11">
+      <c r="A72" t="s">
+        <v>81</v>
+      </c>
+      <c r="B72">
+        <v>1</v>
+      </c>
+      <c r="C72">
+        <v>1.94</v>
+      </c>
+      <c r="D72">
+        <v>1.19</v>
+      </c>
+      <c r="E72">
+        <v>2.96</v>
+      </c>
+      <c r="H72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>449</v>
+      </c>
+      <c r="K72">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11">
+      <c r="A73" t="s">
+        <v>82</v>
+      </c>
+      <c r="B73">
+        <v>1</v>
+      </c>
+      <c r="C73">
         <v>3.71</v>
       </c>
-      <c r="D61">
+      <c r="D73">
         <v>2.67</v>
       </c>
-      <c r="E61">
+      <c r="E73">
         <v>4.78</v>
       </c>
-      <c r="H61">
+      <c r="H73">
         <v>0</v>
       </c>
-      <c r="J61">
+      <c r="J73">
         <v>718</v>
       </c>
-      <c r="K61">
+      <c r="K73">
         <v>358</v>
       </c>
     </row>

--- a/exposures_meta_analysis_final_combined.xlsx
+++ b/exposures_meta_analysis_final_combined.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,61 +425,61 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K72"/>
+  <dimension ref="A1:K71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Exposure</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>number studies</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Pooled RR</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>lower CI RR</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>upper CI RR</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>lower PI RR</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>upper PI RR</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>I^2 (%)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eggers p-value</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>total N</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>total Cases</t>
         </is>
@@ -563,7 +575,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4575581064437778</v>
+        <v>0.4575581064437775</v>
       </c>
       <c r="J4" t="n">
         <v>3660</v>
@@ -637,32 +649,38 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>papaya</t>
+          <t>vitamin_b6</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C7" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>0.37</v>
+        <v>0.42</v>
       </c>
       <c r="E7" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+        <v>0.76</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.43</v>
+      </c>
       <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="inlineStr"/>
+        <v>72.2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.006929997867264431</v>
+      </c>
       <c r="J7" t="n">
-        <v>876</v>
+        <v>92079</v>
       </c>
       <c r="K7" t="n">
-        <v>438</v>
+        <v>3337</v>
       </c>
     </row>
     <row r="8">
@@ -693,7 +711,7 @@
         <v>94.5</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8351773861379138</v>
+        <v>0.8351773861379139</v>
       </c>
       <c r="J8" t="n">
         <v>5809</v>
@@ -705,38 +723,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>vitamin_b6</t>
+          <t>papaya</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>0.42</v>
+        <v>0.37</v>
       </c>
       <c r="E9" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1.43</v>
-      </c>
+        <v>0.84</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>72.2</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.006929997867264431</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>92079</v>
+        <v>876</v>
       </c>
       <c r="K9" t="n">
-        <v>3337</v>
+        <v>438</v>
       </c>
     </row>
     <row r="10">
@@ -767,7 +779,7 @@
         <v>94.09999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>0.001758518003460142</v>
+        <v>0.001758518003460143</v>
       </c>
       <c r="J10" t="n">
         <v>273560</v>
@@ -841,75 +853,75 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>lutein</t>
+          <t>omega-3_fatty_acids</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
         <v>0.65</v>
       </c>
       <c r="D13" t="n">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>0.78</v>
+        <v>0.76</v>
       </c>
       <c r="F13" t="n">
         <v>0.36</v>
       </c>
       <c r="G13" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="H13" t="n">
-        <v>79.90000000000001</v>
+        <v>68</v>
       </c>
       <c r="I13" t="n">
-        <v>0.009603755584594278</v>
+        <v>0.5929735955651932</v>
       </c>
       <c r="J13" t="n">
-        <v>1067447</v>
+        <v>242088</v>
       </c>
       <c r="K13" t="n">
-        <v>48416</v>
+        <v>10615</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>omega-3_fatty_acids</t>
+          <t>lutein</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C14" t="n">
         <v>0.65</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="E14" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="F14" t="n">
         <v>0.36</v>
       </c>
       <c r="G14" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="H14" t="n">
-        <v>68</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5929735955651932</v>
+        <v>0.009603755584594274</v>
       </c>
       <c r="J14" t="n">
-        <v>242088</v>
+        <v>1067447</v>
       </c>
       <c r="K14" t="n">
-        <v>10615</v>
+        <v>48416</v>
       </c>
     </row>
     <row r="15">
@@ -940,7 +952,7 @@
         <v>87.3</v>
       </c>
       <c r="I15" t="n">
-        <v>0.02220092332067387</v>
+        <v>0.02220092332067385</v>
       </c>
       <c r="J15" t="n">
         <v>88794</v>
@@ -952,131 +964,131 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>iodine</t>
+          <t>lycopene</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
         <v>0.68</v>
       </c>
       <c r="D16" t="n">
-        <v>0.46</v>
+        <v>0.55</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+        <v>0.84</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.43</v>
+      </c>
       <c r="H16" t="n">
-        <v>44.9</v>
-      </c>
-      <c r="I16" t="inlineStr"/>
+        <v>82.8</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.1176939329825924</v>
+      </c>
       <c r="J16" t="n">
-        <v>3284</v>
+        <v>334206</v>
       </c>
       <c r="K16" t="n">
-        <v>1288</v>
+        <v>132822</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>lycopene</t>
+          <t>iodine</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C17" t="n">
         <v>0.68</v>
       </c>
       <c r="D17" t="n">
-        <v>0.55</v>
+        <v>0.46</v>
       </c>
       <c r="E17" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1.43</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>82.8</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.1176939329825923</v>
-      </c>
+        <v>44.9</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="n">
-        <v>334206</v>
+        <v>3284</v>
       </c>
       <c r="K17" t="n">
-        <v>132822</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>oats</t>
+          <t>n-acetylcysteine</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
         <v>0.7</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3</v>
+        <v>0.68</v>
       </c>
       <c r="E18" t="n">
-        <v>1.65</v>
+        <v>0.73</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>82.3</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
-        <v>28604</v>
+        <v>91546</v>
       </c>
       <c r="K18" t="n">
-        <v>1075</v>
+        <v>11901</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>n-acetylcysteine</t>
+          <t>oats</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
         <v>0.7</v>
       </c>
       <c r="D19" t="n">
-        <v>0.68</v>
+        <v>0.3</v>
       </c>
       <c r="E19" t="n">
-        <v>0.73</v>
+        <v>1.65</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>82.3</v>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
-        <v>91546</v>
+        <v>28604</v>
       </c>
       <c r="K19" t="n">
-        <v>11901</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="20">
@@ -1107,7 +1119,7 @@
         <v>44.2</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1879066502188127</v>
+        <v>0.1879066502188126</v>
       </c>
       <c r="J20" t="n">
         <v>243855</v>
@@ -1144,7 +1156,7 @@
         <v>84.2</v>
       </c>
       <c r="I21" t="n">
-        <v>0.02221627450015601</v>
+        <v>0.022216274500156</v>
       </c>
       <c r="J21" t="n">
         <v>856523</v>
@@ -1181,7 +1193,7 @@
         <v>87</v>
       </c>
       <c r="I22" t="n">
-        <v>2.930546567262836e-05</v>
+        <v>2.930546567262832e-05</v>
       </c>
       <c r="J22" t="n">
         <v>540284</v>
@@ -1218,7 +1230,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>0.01919136648399248</v>
+        <v>0.01919136648399242</v>
       </c>
       <c r="J23" t="n">
         <v>984463</v>
@@ -1286,7 +1298,7 @@
         <v>82.40000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>0.02000889385459848</v>
+        <v>0.02000889385459846</v>
       </c>
       <c r="J25" t="n">
         <v>508427</v>
@@ -1360,7 +1372,7 @@
         <v>81.90000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1779303397630421</v>
+        <v>0.177930339763042</v>
       </c>
       <c r="J27" t="n">
         <v>77198</v>
@@ -1397,7 +1409,7 @@
         <v>89.40000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>0.09603493939892219</v>
+        <v>0.0960349393989222</v>
       </c>
       <c r="J28" t="n">
         <v>1382343</v>
@@ -1440,75 +1452,75 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>miso</t>
+          <t>olive</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C30" t="n">
         <v>0.8</v>
       </c>
       <c r="D30" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>1.13</v>
+        <v>0.92</v>
       </c>
       <c r="F30" t="n">
-        <v>0.02</v>
+        <v>0.51</v>
       </c>
       <c r="G30" t="n">
-        <v>33.61</v>
+        <v>1.24</v>
       </c>
       <c r="H30" t="n">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="I30" t="n">
-        <v>0.5607534123225344</v>
+        <v>0.01389915282783272</v>
       </c>
       <c r="J30" t="n">
-        <v>87065</v>
+        <v>248595</v>
       </c>
       <c r="K30" t="n">
-        <v>751</v>
+        <v>16870</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>olive</t>
+          <t>miso</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C31" t="n">
         <v>0.8</v>
       </c>
       <c r="D31" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>0.92</v>
+        <v>1.13</v>
       </c>
       <c r="F31" t="n">
-        <v>0.51</v>
+        <v>0.02</v>
       </c>
       <c r="G31" t="n">
-        <v>1.24</v>
+        <v>33.61</v>
       </c>
       <c r="H31" t="n">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="I31" t="n">
-        <v>0.01389915282783273</v>
+        <v>0.5607534123225345</v>
       </c>
       <c r="J31" t="n">
-        <v>248595</v>
+        <v>87065</v>
       </c>
       <c r="K31" t="n">
-        <v>16870</v>
+        <v>751</v>
       </c>
     </row>
     <row r="32">
@@ -1551,162 +1563,156 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>non-alcoholic_fermented_foods</t>
+          <t>flax</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="D33" t="n">
-        <v>0.64</v>
+        <v>0.72</v>
       </c>
       <c r="E33" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="G33" t="n">
-        <v>1.98</v>
-      </c>
+        <v>0.97</v>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
-        <v>91.40000000000001</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0.6522742230222329</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="n">
-        <v>143000</v>
+        <v>6369</v>
       </c>
       <c r="K33" t="n">
-        <v>41773</v>
+        <v>2999</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>fermented_foods</t>
+          <t>flaxseed</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C34" t="n">
         <v>0.84</v>
       </c>
       <c r="D34" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="E34" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="G34" t="n">
-        <v>1.1</v>
-      </c>
+        <v>0.97</v>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
-        <v>61.9</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0.006338262199775895</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="n">
-        <v>1687421</v>
+        <v>6369</v>
       </c>
       <c r="K34" t="n">
-        <v>248942</v>
+        <v>2999</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>flaxseed</t>
+          <t>vitamin_d</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C35" t="n">
         <v>0.84</v>
       </c>
       <c r="D35" t="n">
-        <v>0.72</v>
+        <v>0.8</v>
       </c>
       <c r="E35" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
+        <v>0.87</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1.09</v>
+      </c>
       <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="inlineStr"/>
+        <v>84.09999999999999</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.78404157923121e-10</v>
+      </c>
       <c r="J35" t="n">
-        <v>6369</v>
+        <v>1597494</v>
       </c>
       <c r="K35" t="n">
-        <v>2999</v>
+        <v>241174</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>vitamin_d</t>
+          <t>melatonin</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="C36" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="D36" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="E36" t="n">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="F36" t="n">
-        <v>0.64</v>
+        <v>0.55</v>
       </c>
       <c r="G36" t="n">
-        <v>1.09</v>
+        <v>1.31</v>
       </c>
       <c r="H36" t="n">
-        <v>84.09999999999999</v>
+        <v>42.3</v>
       </c>
       <c r="I36" t="n">
-        <v>1.784041579231218e-10</v>
+        <v>0.9864318175325137</v>
       </c>
       <c r="J36" t="n">
-        <v>1597494</v>
+        <v>62422</v>
       </c>
       <c r="K36" t="n">
-        <v>241174</v>
+        <v>3175</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>flax</t>
+          <t>manganese</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="D37" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="E37" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
@@ -1715,152 +1721,158 @@
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="n">
-        <v>6369</v>
+        <v>2939</v>
       </c>
       <c r="K37" t="n">
-        <v>2999</v>
+        <v>382</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>melatonin</t>
+          <t>yogurt</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C38" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="D38" t="n">
-        <v>0.73</v>
+        <v>0.79</v>
       </c>
       <c r="E38" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F38" t="n">
-        <v>0.55</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G38" t="n">
-        <v>1.31</v>
+        <v>1.08</v>
       </c>
       <c r="H38" t="n">
-        <v>42.3</v>
+        <v>50.4</v>
       </c>
       <c r="I38" t="n">
-        <v>0.9864318175325135</v>
+        <v>0.01216014445622597</v>
       </c>
       <c r="J38" t="n">
-        <v>62422</v>
+        <v>1587902</v>
       </c>
       <c r="K38" t="n">
-        <v>3175</v>
+        <v>244079</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>manganese</t>
+          <t>fermented_foods</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C39" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="D39" t="n">
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
       <c r="E39" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
+        <v>1.03</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1.66</v>
+      </c>
       <c r="H39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.5843314822907089</v>
+      </c>
       <c r="J39" t="n">
-        <v>2939</v>
+        <v>1787554</v>
       </c>
       <c r="K39" t="n">
-        <v>382</v>
+        <v>250200</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>yogurt</t>
+          <t>vitamin_a</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C40" t="n">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="D40" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="E40" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.08</v>
       </c>
       <c r="F40" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.46</v>
       </c>
       <c r="G40" t="n">
-        <v>1.08</v>
+        <v>1.8</v>
       </c>
       <c r="H40" t="n">
-        <v>50.4</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="I40" t="n">
-        <v>0.01216014445622596</v>
+        <v>0.4889561242721966</v>
       </c>
       <c r="J40" t="n">
-        <v>1587902</v>
+        <v>580493</v>
       </c>
       <c r="K40" t="n">
-        <v>244079</v>
+        <v>144042</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>vitamin_a</t>
+          <t>calcium</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="C41" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="D41" t="n">
-        <v>0.76</v>
+        <v>0.88</v>
       </c>
       <c r="E41" t="n">
-        <v>1.08</v>
+        <v>0.96</v>
       </c>
       <c r="F41" t="n">
-        <v>0.46</v>
+        <v>0.8</v>
       </c>
       <c r="G41" t="n">
-        <v>1.8</v>
+        <v>1.07</v>
       </c>
       <c r="H41" t="n">
-        <v>85.09999999999999</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>0.4889561242721969</v>
+        <v>0.004626575242725505</v>
       </c>
       <c r="J41" t="n">
-        <v>580493</v>
+        <v>930114</v>
       </c>
       <c r="K41" t="n">
-        <v>144042</v>
+        <v>77262</v>
       </c>
     </row>
     <row r="42">
@@ -1903,38 +1915,38 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>calcium</t>
+          <t>vitamin_e</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C43" t="n">
-        <v>0.92</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="D43" t="n">
-        <v>0.88</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E43" t="n">
-        <v>0.96</v>
+        <v>1.09</v>
       </c>
       <c r="F43" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="G43" t="n">
-        <v>1.07</v>
+        <v>1.74</v>
       </c>
       <c r="H43" t="n">
-        <v>76.90000000000001</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="I43" t="n">
-        <v>0.004626575242725492</v>
+        <v>0.9597674472320056</v>
       </c>
       <c r="J43" t="n">
-        <v>930114</v>
+        <v>746495</v>
       </c>
       <c r="K43" t="n">
-        <v>77262</v>
+        <v>277405</v>
       </c>
     </row>
     <row r="44">
@@ -1965,7 +1977,7 @@
         <v>83</v>
       </c>
       <c r="I44" t="n">
-        <v>0.5612991451474088</v>
+        <v>0.5612991451474085</v>
       </c>
       <c r="J44" t="n">
         <v>512782</v>
@@ -1977,483 +1989,483 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>vitamin_e</t>
+          <t>selenium</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C45" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="D45" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.89</v>
       </c>
       <c r="E45" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="F45" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="G45" t="n">
-        <v>1.74</v>
+        <v>1.23</v>
       </c>
       <c r="H45" t="n">
-        <v>83.59999999999999</v>
+        <v>58.4</v>
       </c>
       <c r="I45" t="n">
-        <v>0.9597674472320058</v>
+        <v>0.9919383665571097</v>
       </c>
       <c r="J45" t="n">
-        <v>746495</v>
+        <v>343803</v>
       </c>
       <c r="K45" t="n">
-        <v>277405</v>
+        <v>20200</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>selenium</t>
+          <t>caffeine</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C46" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="D46" t="n">
-        <v>0.89</v>
+        <v>0.92</v>
       </c>
       <c r="E46" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="F46" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="G46" t="n">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="H46" t="n">
-        <v>58.4</v>
+        <v>45.9</v>
       </c>
       <c r="I46" t="n">
-        <v>0.9919383665571097</v>
+        <v>0.4259906328747258</v>
       </c>
       <c r="J46" t="n">
-        <v>343803</v>
+        <v>872194</v>
       </c>
       <c r="K46" t="n">
-        <v>20200</v>
+        <v>38461</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>caffeine</t>
+          <t>bcaas</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C47" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="D47" t="n">
-        <v>0.92</v>
+        <v>0.87</v>
       </c>
       <c r="E47" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="F47" t="n">
-        <v>0.85</v>
+        <v>0.25</v>
       </c>
       <c r="G47" t="n">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
       <c r="H47" t="n">
-        <v>45.9</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="I47" t="n">
-        <v>0.4259906328747252</v>
+        <v>0.2941582730123408</v>
       </c>
       <c r="J47" t="n">
-        <v>872194</v>
+        <v>223922</v>
       </c>
       <c r="K47" t="n">
-        <v>38461</v>
+        <v>13868</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcaas</t>
+          <t>dairy</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="C48" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" t="n">
         <v>0.98</v>
       </c>
-      <c r="D48" t="n">
-        <v>0.87</v>
-      </c>
       <c r="E48" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G48" t="n">
         <v>1.1</v>
       </c>
-      <c r="F48" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G48" t="n">
-        <v>3.8</v>
-      </c>
       <c r="H48" t="n">
-        <v>85.59999999999999</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I48" t="n">
-        <v>0.2941582730123409</v>
+        <v>0.6133032909092402</v>
       </c>
       <c r="J48" t="n">
-        <v>223922</v>
+        <v>4496801</v>
       </c>
       <c r="K48" t="n">
-        <v>13868</v>
+        <v>406240</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>dairy</t>
+          <t>isoleucine</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="C49" t="n">
         <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>0.98</v>
+        <v>0.87</v>
       </c>
       <c r="E49" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="F49" t="n">
-        <v>0.91</v>
+        <v>0.57</v>
       </c>
       <c r="G49" t="n">
-        <v>1.1</v>
+        <v>1.74</v>
       </c>
       <c r="H49" t="n">
-        <v>88.40000000000001</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="I49" t="n">
-        <v>0.6133032909092403</v>
+        <v>0.9376775415524358</v>
       </c>
       <c r="J49" t="n">
-        <v>4496801</v>
+        <v>227916</v>
       </c>
       <c r="K49" t="n">
-        <v>406240</v>
+        <v>15865</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>isoleucine</t>
+          <t>vitamin_k</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="D50" t="n">
-        <v>0.87</v>
+        <v>0.68</v>
       </c>
       <c r="E50" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="F50" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="G50" t="n">
-        <v>1.74</v>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
-        <v>86.09999999999999</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0.9376775415524358</v>
-      </c>
+        <v>91.8</v>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="n">
-        <v>227916</v>
+        <v>5048</v>
       </c>
       <c r="K50" t="n">
-        <v>15865</v>
+        <v>2592</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>vitamin_k</t>
+          <t>tea</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="C51" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="D51" t="n">
-        <v>0.68</v>
+        <v>0.98</v>
       </c>
       <c r="E51" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
+        <v>1.07</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G51" t="n">
+        <v>1.18</v>
+      </c>
       <c r="H51" t="n">
-        <v>91.8</v>
-      </c>
-      <c r="I51" t="inlineStr"/>
+        <v>90.5</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.9812909136692176</v>
+      </c>
       <c r="J51" t="n">
-        <v>5048</v>
+        <v>1887493</v>
       </c>
       <c r="K51" t="n">
-        <v>2592</v>
+        <v>232708</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>tea</t>
+          <t>quercetin</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="D52" t="n">
-        <v>0.98</v>
+        <v>0.83</v>
       </c>
       <c r="E52" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="F52" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="G52" t="n">
-        <v>1.18</v>
-      </c>
+        <v>1.34</v>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
-        <v>90.5</v>
-      </c>
-      <c r="I52" t="n">
-        <v>0.9812909136692176</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="J52" t="n">
-        <v>1887493</v>
+        <v>90630</v>
       </c>
       <c r="K52" t="n">
-        <v>232708</v>
+        <v>710</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>quercetin</t>
+          <t>conjugated_linoleic_acid</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C53" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="D53" t="n">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="E53" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
+        <v>1.22</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1.82</v>
+      </c>
       <c r="H53" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" t="inlineStr"/>
+        <v>62</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.4225544208553844</v>
+      </c>
       <c r="J53" t="n">
-        <v>90630</v>
+        <v>380443</v>
       </c>
       <c r="K53" t="n">
-        <v>710</v>
+        <v>17329</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>conjugated_linoleic_acid</t>
+          <t>glucosamine</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C54" t="n">
         <v>1.06</v>
       </c>
       <c r="D54" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="E54" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="F54" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="G54" t="n">
-        <v>1.82</v>
-      </c>
+        <v>1.21</v>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
-        <v>62</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0.4225544208553845</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="n">
-        <v>380443</v>
+        <v>41082</v>
       </c>
       <c r="K54" t="n">
-        <v>17329</v>
+        <v>5341</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>glucosamine</t>
+          <t>leucine</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C55" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="D55" t="n">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="E55" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>40.5</v>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="n">
-        <v>41082</v>
+        <v>28476</v>
       </c>
       <c r="K55" t="n">
-        <v>5341</v>
+        <v>5237</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>leucine</t>
+          <t>grapefruit</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>2</v>
       </c>
       <c r="C56" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="D56" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="E56" t="n">
-        <v>1.2</v>
+        <v>1.52</v>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
-        <v>40.5</v>
+        <v>82.8</v>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="n">
-        <v>28476</v>
+        <v>164504</v>
       </c>
       <c r="K56" t="n">
-        <v>5237</v>
+        <v>5404</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>grapefruit</t>
+          <t>creatine</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C57" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="D57" t="n">
-        <v>0.8</v>
+        <v>1.01</v>
       </c>
       <c r="E57" t="n">
-        <v>1.52</v>
+        <v>1.19</v>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
-        <v>82.8</v>
+        <v>0</v>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="n">
-        <v>164504</v>
+        <v>207</v>
       </c>
       <c r="K57" t="n">
-        <v>5404</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>creatine</t>
+          <t>carnitine</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C58" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="D58" t="n">
-        <v>1.01</v>
+        <v>0.9</v>
       </c>
       <c r="E58" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
+        <v>1.41</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="G58" t="n">
+        <v>3.02</v>
+      </c>
       <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="inlineStr"/>
+        <v>82.8</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.7636681889414908</v>
+      </c>
       <c r="J58" t="n">
-        <v>207</v>
+        <v>384266</v>
       </c>
       <c r="K58" t="n">
-        <v>1057</v>
+        <v>140082</v>
       </c>
     </row>
     <row r="59">
@@ -2484,7 +2496,7 @@
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>0.9877864190999567</v>
+        <v>0.987786419099957</v>
       </c>
       <c r="J59" t="n">
         <v>66508</v>
@@ -2496,7 +2508,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>carnitine</t>
+          <t>magnesium</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -2506,300 +2518,294 @@
         <v>1.13</v>
       </c>
       <c r="D60" t="n">
-        <v>0.9</v>
+        <v>0.97</v>
       </c>
       <c r="E60" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="F60" t="n">
-        <v>0.42</v>
+        <v>0.58</v>
       </c>
       <c r="G60" t="n">
-        <v>3.02</v>
+        <v>2.19</v>
       </c>
       <c r="H60" t="n">
-        <v>82.8</v>
+        <v>83.8</v>
       </c>
       <c r="I60" t="n">
-        <v>0.7636681889414909</v>
+        <v>0.9619708795552824</v>
       </c>
       <c r="J60" t="n">
-        <v>384266</v>
+        <v>1172319</v>
       </c>
       <c r="K60" t="n">
-        <v>140082</v>
+        <v>257639</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>magnesium</t>
+          <t>zinc</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C61" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="D61" t="n">
-        <v>0.97</v>
+        <v>0.68</v>
       </c>
       <c r="E61" t="n">
-        <v>1.32</v>
+        <v>1.91</v>
       </c>
       <c r="F61" t="n">
-        <v>0.58</v>
+        <v>0.16</v>
       </c>
       <c r="G61" t="n">
-        <v>2.19</v>
+        <v>8.09</v>
       </c>
       <c r="H61" t="n">
-        <v>83.8</v>
+        <v>96</v>
       </c>
       <c r="I61" t="n">
-        <v>0.9619708795552824</v>
+        <v>0.6073544042976851</v>
       </c>
       <c r="J61" t="n">
-        <v>1172319</v>
+        <v>119440</v>
       </c>
       <c r="K61" t="n">
-        <v>257639</v>
+        <v>10103</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>zinc</t>
+          <t>iron</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C62" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="D62" t="n">
-        <v>0.68</v>
+        <v>1.06</v>
       </c>
       <c r="E62" t="n">
-        <v>1.91</v>
+        <v>1.25</v>
       </c>
       <c r="F62" t="n">
-        <v>0.16</v>
+        <v>0.84</v>
       </c>
       <c r="G62" t="n">
-        <v>8.09</v>
+        <v>1.58</v>
       </c>
       <c r="H62" t="n">
-        <v>96</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I62" t="n">
-        <v>0.6073544042976849</v>
+        <v>0.1723925153093609</v>
       </c>
       <c r="J62" t="n">
-        <v>119440</v>
+        <v>1376214</v>
       </c>
       <c r="K62" t="n">
-        <v>10103</v>
+        <v>221434</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>iron</t>
+          <t>eggs</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C63" t="n">
         <v>1.15</v>
       </c>
       <c r="D63" t="n">
-        <v>1.06</v>
+        <v>0.95</v>
       </c>
       <c r="E63" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="F63" t="n">
-        <v>0.84</v>
+        <v>0.67</v>
       </c>
       <c r="G63" t="n">
-        <v>1.58</v>
+        <v>1.96</v>
       </c>
       <c r="H63" t="n">
-        <v>80.59999999999999</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I63" t="n">
-        <v>0.1723925153093609</v>
+        <v>0.7478766568479689</v>
       </c>
       <c r="J63" t="n">
-        <v>1376214</v>
+        <v>29487</v>
       </c>
       <c r="K63" t="n">
-        <v>221434</v>
+        <v>5481</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>eggs</t>
+          <t>red_meat</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C64" t="n">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="D64" t="n">
-        <v>0.95</v>
+        <v>1.2</v>
       </c>
       <c r="E64" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="F64" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="G64" t="n">
-        <v>1.96</v>
+        <v>1.6</v>
       </c>
       <c r="H64" t="n">
-        <v>86.59999999999999</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I64" t="n">
-        <v>0.7478766568479689</v>
+        <v>3.550216935243029e-10</v>
       </c>
       <c r="J64" t="n">
-        <v>29487</v>
+        <v>1188831</v>
       </c>
       <c r="K64" t="n">
-        <v>5481</v>
+        <v>70016</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>red_meat</t>
+          <t>dehydroepiandrosterone</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C65" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="D65" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="E65" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="F65" t="n">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="G65" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="H65" t="n">
-        <v>88.40000000000001</v>
+        <v>65.3</v>
       </c>
       <c r="I65" t="n">
-        <v>3.550216935243042e-10</v>
+        <v>0.0001090796573211561</v>
       </c>
       <c r="J65" t="n">
-        <v>1188831</v>
+        <v>248188</v>
       </c>
       <c r="K65" t="n">
-        <v>70016</v>
+        <v>127366</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>dehydroepiandrosterone</t>
+          <t>phosphorus</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C66" t="n">
         <v>1.27</v>
       </c>
       <c r="D66" t="n">
-        <v>1.16</v>
+        <v>0.49</v>
       </c>
       <c r="E66" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="F66" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="G66" t="n">
-        <v>1.68</v>
-      </c>
+        <v>3.26</v>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
-        <v>65.3</v>
-      </c>
-      <c r="I66" t="n">
-        <v>0.0001090796573211565</v>
-      </c>
+        <v>78.2</v>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="J66" t="n">
-        <v>248188</v>
+        <v>229321</v>
       </c>
       <c r="K66" t="n">
-        <v>127366</v>
+        <v>123051</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>phosphorus</t>
+          <t>glutamine</t>
         </is>
       </c>
       <c r="B67" t="n">
         <v>2</v>
       </c>
       <c r="C67" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="D67" t="n">
-        <v>0.49</v>
+        <v>1.12</v>
       </c>
       <c r="E67" t="n">
-        <v>3.26</v>
+        <v>1.55</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
-        <v>78.2</v>
+        <v>0</v>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="n">
-        <v>229321</v>
+        <v>1024</v>
       </c>
       <c r="K67" t="n">
-        <v>123051</v>
+        <v>417</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>glutamine</t>
+          <t>cannabidiol</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C68" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="D68" t="n">
-        <v>1.12</v>
+        <v>1.39</v>
       </c>
       <c r="E68" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr"/>
@@ -2808,97 +2814,97 @@
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="n">
-        <v>1024</v>
+        <v>124896418350</v>
       </c>
       <c r="K68" t="n">
-        <v>417</v>
+        <v>51623922</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>cannabidiol</t>
+          <t>copper</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C69" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="D69" t="n">
-        <v>1.39</v>
+        <v>0.95</v>
       </c>
       <c r="E69" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
+        <v>2.31</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="G69" t="n">
+        <v>6.92</v>
+      </c>
       <c r="H69" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" t="inlineStr"/>
+        <v>87.3</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.6033187907654798</v>
+      </c>
       <c r="J69" t="n">
-        <v>124896418350</v>
+        <v>65169</v>
       </c>
       <c r="K69" t="n">
-        <v>51623922</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>copper</t>
+          <t>coenzyme_q10</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C70" t="n">
-        <v>1.49</v>
+        <v>1.94</v>
       </c>
       <c r="D70" t="n">
-        <v>0.95</v>
+        <v>1.19</v>
       </c>
       <c r="E70" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="F70" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="G70" t="n">
-        <v>6.92</v>
-      </c>
+        <v>2.96</v>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
-        <v>87.3</v>
-      </c>
-      <c r="I70" t="n">
-        <v>0.60331879076548</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="J70" t="n">
-        <v>65169</v>
+        <v>449</v>
       </c>
       <c r="K70" t="n">
-        <v>1638</v>
+        <v>160</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>coenzyme_q10</t>
+          <t>pickled_vegetables</t>
         </is>
       </c>
       <c r="B71" t="n">
         <v>1</v>
       </c>
       <c r="C71" t="n">
-        <v>1.94</v>
+        <v>3.71</v>
       </c>
       <c r="D71" t="n">
-        <v>1.19</v>
+        <v>2.67</v>
       </c>
       <c r="E71" t="n">
-        <v>2.96</v>
+        <v>4.78</v>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr"/>
@@ -2907,40 +2913,9 @@
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="n">
-        <v>449</v>
+        <v>718</v>
       </c>
       <c r="K71" t="n">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>pickled_vegetables</t>
-        </is>
-      </c>
-      <c r="B72" t="n">
-        <v>1</v>
-      </c>
-      <c r="C72" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="D72" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="E72" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="n">
-        <v>718</v>
-      </c>
-      <c r="K72" t="n">
         <v>358</v>
       </c>
     </row>

--- a/exposures_meta_analysis_final_combined.xlsx
+++ b/exposures_meta_analysis_final_combined.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K71"/>
+  <dimension ref="A1:K70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1131,75 +1131,75 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>antioxidants</t>
+          <t>mediterranean_diet</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C21" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="D21" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="E21" t="n">
-        <v>0.84</v>
+        <v>0.79</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4</v>
+        <v>0.46</v>
       </c>
       <c r="G21" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="H21" t="n">
-        <v>84.2</v>
+        <v>87.2</v>
       </c>
       <c r="I21" t="n">
-        <v>0.022216274500156</v>
+        <v>5.466290886526607e-05</v>
       </c>
       <c r="J21" t="n">
-        <v>856523</v>
+        <v>539860</v>
       </c>
       <c r="K21" t="n">
-        <v>267423</v>
+        <v>28634</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>mediterranean_diet</t>
+          <t>antioxidants</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C22" t="n">
-        <v>0.74</v>
+        <v>0.72</v>
       </c>
       <c r="D22" t="n">
-        <v>0.67</v>
+        <v>0.61</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.84</v>
       </c>
       <c r="F22" t="n">
-        <v>0.51</v>
+        <v>0.4</v>
       </c>
       <c r="G22" t="n">
-        <v>1.07</v>
+        <v>1.3</v>
       </c>
       <c r="H22" t="n">
-        <v>87</v>
+        <v>84.2</v>
       </c>
       <c r="I22" t="n">
-        <v>2.930546567262832e-05</v>
+        <v>0.022216274500156</v>
       </c>
       <c r="J22" t="n">
-        <v>540284</v>
+        <v>856523</v>
       </c>
       <c r="K22" t="n">
-        <v>28689</v>
+        <v>267423</v>
       </c>
     </row>
     <row r="23">
@@ -1209,34 +1209,34 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C23" t="n">
-        <v>0.75</v>
+        <v>0.73</v>
       </c>
       <c r="D23" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="E23" t="n">
-        <v>0.86</v>
+        <v>0.84</v>
       </c>
       <c r="F23" t="n">
         <v>0.32</v>
       </c>
       <c r="G23" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="H23" t="n">
-        <v>90.59999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>0.01919136648399242</v>
+        <v>0.009728933199444161</v>
       </c>
       <c r="J23" t="n">
-        <v>984463</v>
+        <v>982724</v>
       </c>
       <c r="K23" t="n">
-        <v>44792</v>
+        <v>44523</v>
       </c>
     </row>
     <row r="24">
@@ -1421,180 +1421,180 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>cod_liver_oil</t>
+          <t>bcaas</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>2</v>
       </c>
       <c r="C29" t="n">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="D29" t="n">
-        <v>0.68</v>
+        <v>0.4</v>
       </c>
       <c r="E29" t="n">
-        <v>0.9</v>
+        <v>1.48</v>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>92.8</v>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="n">
-        <v>4001</v>
+        <v>197211</v>
       </c>
       <c r="K29" t="n">
-        <v>1731</v>
+        <v>10396</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>olive</t>
+          <t>cod_liver_oil</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
       <c r="D30" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="E30" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="G30" t="n">
-        <v>1.24</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
-        <v>81</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0.01389915282783272</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="n">
-        <v>248595</v>
+        <v>4001</v>
       </c>
       <c r="K30" t="n">
-        <v>16870</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>miso</t>
+          <t>olive</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C31" t="n">
         <v>0.8</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>1.13</v>
+        <v>0.92</v>
       </c>
       <c r="F31" t="n">
-        <v>0.02</v>
+        <v>0.51</v>
       </c>
       <c r="G31" t="n">
-        <v>33.61</v>
+        <v>1.24</v>
       </c>
       <c r="H31" t="n">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="I31" t="n">
-        <v>0.5607534123225345</v>
+        <v>0.01389915282783272</v>
       </c>
       <c r="J31" t="n">
-        <v>87065</v>
+        <v>248595</v>
       </c>
       <c r="K31" t="n">
-        <v>751</v>
+        <v>16870</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>folic_acid</t>
+          <t>miso</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="C32" t="n">
-        <v>0.82</v>
+        <v>0.8</v>
       </c>
       <c r="D32" t="n">
-        <v>0.74</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>0.92</v>
+        <v>1.13</v>
       </c>
       <c r="F32" t="n">
-        <v>0.46</v>
+        <v>0.02</v>
       </c>
       <c r="G32" t="n">
-        <v>1.48</v>
+        <v>33.61</v>
       </c>
       <c r="H32" t="n">
-        <v>84.5</v>
+        <v>57</v>
       </c>
       <c r="I32" t="n">
-        <v>0.02877266109333387</v>
+        <v>0.5607534123225345</v>
       </c>
       <c r="J32" t="n">
-        <v>1079462</v>
+        <v>87065</v>
       </c>
       <c r="K32" t="n">
-        <v>52354</v>
+        <v>751</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>flax</t>
+          <t>folic_acid</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="C33" t="n">
-        <v>0.84</v>
+        <v>0.82</v>
       </c>
       <c r="D33" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="E33" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
+        <v>0.92</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1.48</v>
+      </c>
       <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="inlineStr"/>
+        <v>84.5</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.02877266109333387</v>
+      </c>
       <c r="J33" t="n">
-        <v>6369</v>
+        <v>1079462</v>
       </c>
       <c r="K33" t="n">
-        <v>2999</v>
+        <v>52354</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>flaxseed</t>
+          <t>flax</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1625,75 +1625,69 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>vitamin_d</t>
+          <t>flaxseed</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="C35" t="n">
         <v>0.84</v>
       </c>
       <c r="D35" t="n">
-        <v>0.8</v>
+        <v>0.72</v>
       </c>
       <c r="E35" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="G35" t="n">
-        <v>1.09</v>
-      </c>
+        <v>0.97</v>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
-        <v>84.09999999999999</v>
-      </c>
-      <c r="I35" t="n">
-        <v>1.78404157923121e-10</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="n">
-        <v>1597494</v>
+        <v>6369</v>
       </c>
       <c r="K35" t="n">
-        <v>241174</v>
+        <v>2999</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>melatonin</t>
+          <t>vitamin_d</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="C36" t="n">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="D36" t="n">
-        <v>0.73</v>
+        <v>0.8</v>
       </c>
       <c r="E36" t="n">
-        <v>1</v>
+        <v>0.87</v>
       </c>
       <c r="F36" t="n">
-        <v>0.55</v>
+        <v>0.64</v>
       </c>
       <c r="G36" t="n">
-        <v>1.31</v>
+        <v>1.09</v>
       </c>
       <c r="H36" t="n">
-        <v>42.3</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>0.9864318175325137</v>
+        <v>1.78404157923121e-10</v>
       </c>
       <c r="J36" t="n">
-        <v>62422</v>
+        <v>1597494</v>
       </c>
       <c r="K36" t="n">
-        <v>3175</v>
+        <v>241174</v>
       </c>
     </row>
     <row r="37">
@@ -1804,149 +1798,149 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>vitamin_a</t>
+          <t>melatonin</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C40" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="D40" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="E40" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="F40" t="n">
-        <v>0.46</v>
+        <v>0.55</v>
       </c>
       <c r="G40" t="n">
-        <v>1.8</v>
+        <v>1.38</v>
       </c>
       <c r="H40" t="n">
-        <v>85.09999999999999</v>
+        <v>45.5</v>
       </c>
       <c r="I40" t="n">
-        <v>0.4889561242721966</v>
+        <v>0.8096930861186756</v>
       </c>
       <c r="J40" t="n">
-        <v>580493</v>
+        <v>28894</v>
       </c>
       <c r="K40" t="n">
-        <v>144042</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>calcium</t>
+          <t>vitamin_a</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C41" t="n">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="D41" t="n">
-        <v>0.88</v>
+        <v>0.76</v>
       </c>
       <c r="E41" t="n">
-        <v>0.96</v>
+        <v>1.08</v>
       </c>
       <c r="F41" t="n">
-        <v>0.8</v>
+        <v>0.46</v>
       </c>
       <c r="G41" t="n">
-        <v>1.07</v>
+        <v>1.8</v>
       </c>
       <c r="H41" t="n">
-        <v>76.90000000000001</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>0.004626575242725505</v>
+        <v>0.4889561242721966</v>
       </c>
       <c r="J41" t="n">
-        <v>930114</v>
+        <v>580493</v>
       </c>
       <c r="K41" t="n">
-        <v>77262</v>
+        <v>144042</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>green_tea</t>
+          <t>calcium</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C42" t="n">
         <v>0.92</v>
       </c>
       <c r="D42" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="E42" t="n">
-        <v>1.05</v>
+        <v>0.96</v>
       </c>
       <c r="F42" t="n">
-        <v>0.61</v>
+        <v>0.8</v>
       </c>
       <c r="G42" t="n">
-        <v>1.39</v>
+        <v>1.07</v>
       </c>
       <c r="H42" t="n">
-        <v>79.40000000000001</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="I42" t="n">
-        <v>0.2347657167208256</v>
+        <v>0.004626575242725505</v>
       </c>
       <c r="J42" t="n">
-        <v>235866</v>
+        <v>930114</v>
       </c>
       <c r="K42" t="n">
-        <v>17930</v>
+        <v>77262</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>vitamin_e</t>
+          <t>green_tea</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C43" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="D43" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="E43" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="F43" t="n">
-        <v>0.5</v>
+        <v>0.61</v>
       </c>
       <c r="G43" t="n">
-        <v>1.74</v>
+        <v>1.39</v>
       </c>
       <c r="H43" t="n">
-        <v>83.59999999999999</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="I43" t="n">
-        <v>0.9597674472320056</v>
+        <v>0.2347657167208256</v>
       </c>
       <c r="J43" t="n">
-        <v>746495</v>
+        <v>235866</v>
       </c>
       <c r="K43" t="n">
-        <v>277405</v>
+        <v>17930</v>
       </c>
     </row>
     <row r="44">
@@ -1989,112 +1983,112 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>selenium</t>
+          <t>vitamin_e</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C45" t="n">
-        <v>0.96</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="D45" t="n">
-        <v>0.89</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E45" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="F45" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="G45" t="n">
-        <v>1.23</v>
+        <v>1.74</v>
       </c>
       <c r="H45" t="n">
-        <v>58.4</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>0.9919383665571097</v>
+        <v>0.9597674472320056</v>
       </c>
       <c r="J45" t="n">
-        <v>343803</v>
+        <v>746495</v>
       </c>
       <c r="K45" t="n">
-        <v>20200</v>
+        <v>277405</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>caffeine</t>
+          <t>selenium</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C46" t="n">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="D46" t="n">
-        <v>0.92</v>
+        <v>0.89</v>
       </c>
       <c r="E46" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="F46" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="G46" t="n">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
       <c r="H46" t="n">
-        <v>45.9</v>
+        <v>58.4</v>
       </c>
       <c r="I46" t="n">
-        <v>0.4259906328747258</v>
+        <v>0.9919383665571097</v>
       </c>
       <c r="J46" t="n">
-        <v>872194</v>
+        <v>343803</v>
       </c>
       <c r="K46" t="n">
-        <v>38461</v>
+        <v>20200</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bcaas</t>
+          <t>caffeine</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C47" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="D47" t="n">
-        <v>0.87</v>
+        <v>0.92</v>
       </c>
       <c r="E47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G47" t="n">
         <v>1.1</v>
       </c>
-      <c r="F47" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G47" t="n">
-        <v>3.8</v>
-      </c>
       <c r="H47" t="n">
-        <v>85.59999999999999</v>
+        <v>45.9</v>
       </c>
       <c r="I47" t="n">
-        <v>0.2941582730123408</v>
+        <v>0.4259906328747258</v>
       </c>
       <c r="J47" t="n">
-        <v>223922</v>
+        <v>872194</v>
       </c>
       <c r="K47" t="n">
-        <v>13868</v>
+        <v>38461</v>
       </c>
     </row>
     <row r="48">
@@ -2242,193 +2236,199 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>quercetin</t>
+          <t>conjugated_linoleic_acid</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C52" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="D52" t="n">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="E52" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
+        <v>1.22</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G52" t="n">
+        <v>1.82</v>
+      </c>
       <c r="H52" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" t="inlineStr"/>
+        <v>62</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.4225544208553844</v>
+      </c>
       <c r="J52" t="n">
-        <v>90630</v>
+        <v>380443</v>
       </c>
       <c r="K52" t="n">
-        <v>710</v>
+        <v>17329</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>conjugated_linoleic_acid</t>
+          <t>glucosamine</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C53" t="n">
         <v>1.06</v>
       </c>
       <c r="D53" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="E53" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="F53" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="G53" t="n">
-        <v>1.82</v>
-      </c>
+        <v>1.21</v>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
-        <v>62</v>
-      </c>
-      <c r="I53" t="n">
-        <v>0.4225544208553844</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="n">
-        <v>380443</v>
+        <v>41082</v>
       </c>
       <c r="K53" t="n">
-        <v>17329</v>
+        <v>5341</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>glucosamine</t>
+          <t>leucine</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C54" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="D54" t="n">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="E54" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>40.5</v>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="n">
-        <v>41082</v>
+        <v>28476</v>
       </c>
       <c r="K54" t="n">
-        <v>5341</v>
+        <v>5237</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>leucine</t>
+          <t>grapefruit</t>
         </is>
       </c>
       <c r="B55" t="n">
         <v>2</v>
       </c>
       <c r="C55" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="D55" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="E55" t="n">
-        <v>1.2</v>
+        <v>1.52</v>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
-        <v>40.5</v>
+        <v>82.8</v>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="n">
-        <v>28476</v>
+        <v>164504</v>
       </c>
       <c r="K55" t="n">
-        <v>5237</v>
+        <v>5404</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>grapefruit</t>
+          <t>creatine</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C56" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="D56" t="n">
-        <v>0.8</v>
+        <v>1.01</v>
       </c>
       <c r="E56" t="n">
-        <v>1.52</v>
+        <v>1.19</v>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
-        <v>82.8</v>
+        <v>0</v>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="n">
-        <v>164504</v>
+        <v>207</v>
       </c>
       <c r="K56" t="n">
-        <v>5404</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>creatine</t>
+          <t>magnesium</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C57" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="D57" t="n">
-        <v>1.01</v>
+        <v>0.97</v>
       </c>
       <c r="E57" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
+        <v>1.32</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="G57" t="n">
+        <v>2.19</v>
+      </c>
       <c r="H57" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" t="inlineStr"/>
+        <v>83.8</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.9619708795552824</v>
+      </c>
       <c r="J57" t="n">
-        <v>207</v>
+        <v>1172319</v>
       </c>
       <c r="K57" t="n">
-        <v>1057</v>
+        <v>257639</v>
       </c>
     </row>
     <row r="58">
@@ -2508,186 +2508,180 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>magnesium</t>
+          <t>zinc</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C60" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="D60" t="n">
-        <v>0.97</v>
+        <v>0.68</v>
       </c>
       <c r="E60" t="n">
-        <v>1.32</v>
+        <v>1.91</v>
       </c>
       <c r="F60" t="n">
-        <v>0.58</v>
+        <v>0.16</v>
       </c>
       <c r="G60" t="n">
-        <v>2.19</v>
+        <v>8.09</v>
       </c>
       <c r="H60" t="n">
-        <v>83.8</v>
+        <v>96</v>
       </c>
       <c r="I60" t="n">
-        <v>0.9619708795552824</v>
+        <v>0.6073544042976851</v>
       </c>
       <c r="J60" t="n">
-        <v>1172319</v>
+        <v>119440</v>
       </c>
       <c r="K60" t="n">
-        <v>257639</v>
+        <v>10103</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>zinc</t>
+          <t>iron</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C61" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="D61" t="n">
-        <v>0.68</v>
+        <v>1.06</v>
       </c>
       <c r="E61" t="n">
-        <v>1.91</v>
+        <v>1.25</v>
       </c>
       <c r="F61" t="n">
-        <v>0.16</v>
+        <v>0.84</v>
       </c>
       <c r="G61" t="n">
-        <v>8.09</v>
+        <v>1.58</v>
       </c>
       <c r="H61" t="n">
-        <v>96</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I61" t="n">
-        <v>0.6073544042976851</v>
+        <v>0.1723925153093609</v>
       </c>
       <c r="J61" t="n">
-        <v>119440</v>
+        <v>1376214</v>
       </c>
       <c r="K61" t="n">
-        <v>10103</v>
+        <v>221434</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>iron</t>
+          <t>eggs</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C62" t="n">
         <v>1.15</v>
       </c>
       <c r="D62" t="n">
-        <v>1.06</v>
+        <v>0.95</v>
       </c>
       <c r="E62" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="F62" t="n">
-        <v>0.84</v>
+        <v>0.67</v>
       </c>
       <c r="G62" t="n">
-        <v>1.58</v>
+        <v>1.96</v>
       </c>
       <c r="H62" t="n">
-        <v>80.59999999999999</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I62" t="n">
-        <v>0.1723925153093609</v>
+        <v>0.7478766568479689</v>
       </c>
       <c r="J62" t="n">
-        <v>1376214</v>
+        <v>29487</v>
       </c>
       <c r="K62" t="n">
-        <v>221434</v>
+        <v>5481</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>eggs</t>
+          <t>red_meat</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C63" t="n">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="D63" t="n">
-        <v>0.95</v>
+        <v>1.2</v>
       </c>
       <c r="E63" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="F63" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>1.96</v>
+        <v>1.6</v>
       </c>
       <c r="H63" t="n">
-        <v>86.59999999999999</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I63" t="n">
-        <v>0.7478766568479689</v>
+        <v>3.550216935243029e-10</v>
       </c>
       <c r="J63" t="n">
-        <v>29487</v>
+        <v>1188831</v>
       </c>
       <c r="K63" t="n">
-        <v>5481</v>
+        <v>70016</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>red_meat</t>
+          <t>phosphorus</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="C64" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="D64" t="n">
-        <v>1.2</v>
+        <v>0.49</v>
       </c>
       <c r="E64" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="F64" t="n">
-        <v>1</v>
-      </c>
-      <c r="G64" t="n">
-        <v>1.6</v>
-      </c>
+        <v>3.26</v>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
-        <v>88.40000000000001</v>
-      </c>
-      <c r="I64" t="n">
-        <v>3.550216935243029e-10</v>
-      </c>
+        <v>78.2</v>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="J64" t="n">
-        <v>1188831</v>
+        <v>229321</v>
       </c>
       <c r="K64" t="n">
-        <v>70016</v>
+        <v>123051</v>
       </c>
     </row>
     <row r="65">
@@ -2730,51 +2724,51 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>phosphorus</t>
+          <t>glutamine</t>
         </is>
       </c>
       <c r="B66" t="n">
         <v>2</v>
       </c>
       <c r="C66" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="D66" t="n">
-        <v>0.49</v>
+        <v>1.12</v>
       </c>
       <c r="E66" t="n">
-        <v>3.26</v>
+        <v>1.55</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
-        <v>78.2</v>
+        <v>0</v>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="n">
-        <v>229321</v>
+        <v>1024</v>
       </c>
       <c r="K66" t="n">
-        <v>123051</v>
+        <v>417</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>glutamine</t>
+          <t>cannabidiol</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C67" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="D67" t="n">
-        <v>1.12</v>
+        <v>1.39</v>
       </c>
       <c r="E67" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
@@ -2783,97 +2777,97 @@
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="n">
-        <v>1024</v>
+        <v>124896418350</v>
       </c>
       <c r="K67" t="n">
-        <v>417</v>
+        <v>51623922</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>cannabidiol</t>
+          <t>copper</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C68" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="D68" t="n">
-        <v>1.39</v>
+        <v>0.95</v>
       </c>
       <c r="E68" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
+        <v>2.31</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="G68" t="n">
+        <v>6.92</v>
+      </c>
       <c r="H68" t="n">
-        <v>0</v>
-      </c>
-      <c r="I68" t="inlineStr"/>
+        <v>87.3</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.6033187907654798</v>
+      </c>
       <c r="J68" t="n">
-        <v>124896418350</v>
+        <v>65169</v>
       </c>
       <c r="K68" t="n">
-        <v>51623922</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>copper</t>
+          <t>coenzyme_q10</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C69" t="n">
-        <v>1.49</v>
+        <v>1.94</v>
       </c>
       <c r="D69" t="n">
-        <v>0.95</v>
+        <v>1.19</v>
       </c>
       <c r="E69" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="F69" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="G69" t="n">
-        <v>6.92</v>
-      </c>
+        <v>2.96</v>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
-        <v>87.3</v>
-      </c>
-      <c r="I69" t="n">
-        <v>0.6033187907654798</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="J69" t="n">
-        <v>65169</v>
+        <v>449</v>
       </c>
       <c r="K69" t="n">
-        <v>1638</v>
+        <v>160</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>coenzyme_q10</t>
+          <t>pickled_vegetables</t>
         </is>
       </c>
       <c r="B70" t="n">
         <v>1</v>
       </c>
       <c r="C70" t="n">
-        <v>1.94</v>
+        <v>3.71</v>
       </c>
       <c r="D70" t="n">
-        <v>1.19</v>
+        <v>2.67</v>
       </c>
       <c r="E70" t="n">
-        <v>2.96</v>
+        <v>4.78</v>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr"/>
@@ -2882,40 +2876,9 @@
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="n">
-        <v>449</v>
+        <v>718</v>
       </c>
       <c r="K70" t="n">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>pickled_vegetables</t>
-        </is>
-      </c>
-      <c r="B71" t="n">
-        <v>1</v>
-      </c>
-      <c r="C71" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="D71" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="E71" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="n">
-        <v>718</v>
-      </c>
-      <c r="K71" t="n">
         <v>358</v>
       </c>
     </row>
